--- a/02_product/02_course_creation/00_curriculum_and_index/Korean Course Curriculum Map_Final_V7.xlsx
+++ b/02_product/02_course_creation/00_curriculum_and_index/Korean Course Curriculum Map_Final_V7.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vault\Koreanwithji_vault\Claude outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vault\Koreanwithji_vault\02_product\02_course_creation\00_curriculum_and_index\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCC86AA-33E7-4F6C-A3DD-3D769A4D06DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D587773-900F-462E-8555-4A698A8B6DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="7500" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curriculum Map" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="레벨1순서update" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="386">
   <si>
     <t>Ji 레벨</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t>Ji 레슨 Title</t>
-  </si>
-  <si>
-    <t>Ji 레슨 주제</t>
   </si>
   <si>
     <t>Draft
@@ -45,12 +42,6 @@
     <t>Video Sales Letter_The Korean Language Core</t>
   </si>
   <si>
-    <t>Course promo
-정식 레슨이 아니라 말그대로 Video Sales Letter
- - overview of teaching philosophy
- - 어떻게든 구매 전환이 많이 일어나게 하는 것이 목표</t>
-  </si>
-  <si>
     <t>O</t>
   </si>
   <si>
@@ -60,52 +51,13 @@
     <t>How to use this course</t>
   </si>
   <si>
-    <t>Course navigation, study tips, pacing
- - 한글 배우고 나서 배워라라는 메시지
- - 강의 기획 윤곽이 다 나오고 난 다음에 제작한다
-  &gt; 각 레슨 별 worksheet 사용방법
-  &gt; Skool community에 질문하라는 안내
-  &gt; 효과적인 학습법 (Input process output)</t>
-  </si>
-  <si>
     <t>How to study vocabulary</t>
   </si>
   <si>
-    <t xml:space="preserve">한국어의 단어 체계
- - Sino-Korean vs Pure Korean vocabulary
-(선택하다 vs 고르다 type pairs)
-context-based learning
- - 단어를 개별적으로 외우려고 들지 말고 full sentence로 공부해라
-  &gt; comprehensible input 소개
-  &gt; 그래야 context를 알 수 있다. 한국어는 high context 언어이다
-  &gt; 같은 단어도 어떤 맥락에서 쓰이느냐에 따라 뜻이 달라진다
-단어 공부법
- - 마케팅 캠페인과 밀접한 연관이 있는 레슨 (marketing_plan.md 참조)
-  &gt; 무료자료 Lead (6000 most Common Korean words)
-  &gt; SRS (Spaced repetition System) 기반 Flashcard app Affiliate marketing으로 부가 수익 창출 </t>
-  </si>
-  <si>
     <t>Hangul</t>
   </si>
   <si>
     <t>Introduction to Hangul</t>
-  </si>
-  <si>
-    <t>Block structure, design logic, vowel/consonant distinction
- - ㅡ being the neutral vowel
- - 외래어 spelling
-  &gt;Stress (1 syllable) → 스트레스 (4 syllables)
-발음 관련 Tip
- - why ㄴ sounds like ㄷ &amp; why ㅁ sounds like ㅂ</t>
-  </si>
-  <si>
-    <t>Types of consonants</t>
-  </si>
-  <si>
-    <t>Plain, tense, aspirated consonants &amp; vowels</t>
-  </si>
-  <si>
-    <t>Batchim &amp; Sound change rules</t>
   </si>
   <si>
     <t>받침 rules, Consonant Assimilation (자음동화)
@@ -147,13 +99,7 @@
     <t>Why Korean has two systems</t>
   </si>
   <si>
-    <t>Sino-Korean numbers</t>
-  </si>
-  <si>
     <t>일, 이, 삼… phone numbers, dates, money</t>
-  </si>
-  <si>
-    <t>Native Korean numbers</t>
   </si>
   <si>
     <t>하나, 둘, 셋… truncation rules</t>
@@ -196,17 +142,6 @@
     <t>Intro to Politeness Level</t>
   </si>
   <si>
-    <t>Politeness level에 대한 전체적인 개념 소개 및 용어 정리
-1. Speech level / Honorific / Humble speech
-Formal high/low
-Informal high/low
-Speech levels (polite 요, casual 반말, formal 니다)
-When to use which speech level &gt; Social, cultural dynamic 설명
- - 언제 반말 쓸 수 있는지
- - Difference between polite (요) VS formal (니다)
- - Plain form 언제 쓰이는지</t>
-  </si>
-  <si>
     <t>One word response</t>
   </si>
   <si>
@@ -223,13 +158,6 @@
   </si>
   <si>
     <t>Verb 101 &amp; Present Tense Conjugation</t>
-  </si>
-  <si>
-    <t>Descriptive Verbs &amp; Action Verbs
-아/어 conjugation rules, 하다→해요
-Important Verbs 하다
- - 하다 Verb 설명 (Sino-Korean verbs all end in 하다)
-compound verbs &amp; connectors 간략히 소개만</t>
   </si>
   <si>
     <t>Past Tense Pt.1 - Conjugation</t>
@@ -271,24 +199,6 @@
     <t>A is B - To be 이다</t>
   </si>
   <si>
-    <t>이것/저것/그것
- - 이것은 OO예요.
- - 이것은 → 이거는 → 이건 Contraction 설명
-이다 VS 있다
- - 에 있다 보여주면서 location marker "에" 간략히만 소개
-이다 conjugation 방법
- - (이)야
- - 이에요 / 예요
- - 입니다
-몇 살이예요? VS 나이가 어떻게 되세요?
-이름이 뭐예요? VS 성함이 어떻게 되세요?
- - "되다"는 become이라는 뜻이지만 "어떻게 되세요? 를 통째로 외워라
- - "되다"의 여러 사용법에 대해서는 추후 배우게 될 것
-제 이름은 OOO예요.
- - 은/는 개념에 대해 간략히만 소개
- - 은/는 받침유무에 따라 변경됨 설명</t>
-  </si>
-  <si>
     <t>To NOT be - 아니다 - This is NOT A</t>
   </si>
   <si>
@@ -299,24 +209,7 @@
     <t>Pronouns &amp; Possessive &amp; Plural</t>
   </si>
   <si>
-    <t>나/저, 우리/저희, 너, 얘/쟤/걔, 이 분/저 분/그 분
- - Don't use 그 and 그녀
-의, contractions (나의→내, 저의→제, 너의→네→니);
-의 vs 네 possessive markers
-들 marker, when optional, 들 on non-nouns, 들 after phrases</t>
-  </si>
-  <si>
     <t>You in Korean</t>
-  </si>
-  <si>
-    <t>Why Korean avoids direct "you"; using titles, names, 오빠/언니/형/누나, when NOT to use 당신
-Honorific Family Titles
- - 어머님, 아버님, 아드님, etc
-형, 오빠, 누나, 언니
-그쪽
-씨 vs 님
-성재는, 태훈이는
-성재야, 태훈아</t>
   </si>
   <si>
     <t>Questions</t>
@@ -333,11 +226,6 @@
   </si>
   <si>
     <t>Basic Phrases - Greetings, Thank you, Sorry, Excuse me</t>
-  </si>
-  <si>
-    <t>안녕하세요, 안녕히 가세요/계세요, 식사하셨어요, pattern recognition across speech levels
-감사합니다/고마워, 죄송합니다/미안해, 실례합니다/저기요
-반갑다 hidden meaning</t>
   </si>
   <si>
     <t>Negative Sentences</t>
@@ -779,9 +667,6 @@
     <t>설마, 혹시, 역시, 굳이, 막, 무조건, 아무래도, 당연히, 하필, 이/저/그대로, 나름(대로), 딱</t>
   </si>
   <si>
-    <t>Onomatopoeia &amp; Mimetic words + Verb</t>
-  </si>
-  <si>
     <t>의성어, 의태어 개념
  - 보글보글
 의성어, 의태어 + 거리다 &amp; 대다
@@ -946,9 +831,6 @@
  - 은/ㄴ 채로</t>
   </si>
   <si>
-    <t>Time &amp; Place #4 - Takes time, Has been time</t>
-  </si>
-  <si>
     <t>Time+ 만에 (간만에 / 오랜만에)
  - ex: 하루만에, 두 시간만에
 It takes time to - 는 데(에) 걸리다
@@ -1248,9 +1130,6 @@
     <t>이리히기 suffix 룰</t>
   </si>
   <si>
-    <t>Verb → Noun #1</t>
-  </si>
-  <si>
     <t>레벨 7: 한국어 동사의 다양한 형태와 Causative Verb를 배울 것
  - Mod + 것 (하는 것)
 ~는/ㄴ/은 거다 (것이다) - ex: 가는거야
@@ -1258,40 +1137,22 @@
  - Mod + ㅁ/음 함</t>
   </si>
   <si>
-    <t>Easy &amp; hard to do</t>
-  </si>
-  <si>
     <t>기(가) 쉽다, 어렵다
 기에</t>
   </si>
   <si>
-    <t>Before &amp; After &amp; Since</t>
-  </si>
-  <si>
     <t>기 전, ㄴ/은 후, 고 나서, 고 나니까, 고 보니까, 고 나면; 끝에 "at the end of". ㄴ/은 이래로</t>
   </si>
   <si>
-    <t>Start &amp; Stop doing</t>
-  </si>
-  <si>
     <t>기 시작하다, 그만하다</t>
-  </si>
-  <si>
-    <t>Decide to do</t>
   </si>
   <si>
     <t>기로 하다
 기로 정하다, 결정하다, 약속하다, etc</t>
   </si>
   <si>
-    <t>To hope</t>
-  </si>
-  <si>
     <t>기를 바라다
  - 면 좋겠다</t>
-  </si>
-  <si>
-    <t>기 + Markers (는, 도, 만)</t>
   </si>
   <si>
     <t>기는 하다, 기도 하다, 기만 하다
@@ -1299,22 +1160,13 @@
  &gt; 하긴요</t>
   </si>
   <si>
-    <t>Adverbs #7 - Descriptive Verb → Adverb - 게</t>
-  </si>
-  <si>
     <t>Verb stem + 게 - So that
  - 모든 Adverb가 ~게로 끝나는 게 아니기 때문에 Adverb는 단어 하나씩 별도로 배울 것</t>
-  </si>
-  <si>
-    <t>End up doing</t>
   </si>
   <si>
     <t>고 말다
  - 고 말았다 VS 고 말겠다
 게 되다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">So that - 게 other usages &amp; 도록 </t>
   </si>
   <si>
     <t>Let &amp; Make someone
@@ -1322,9 +1174,6 @@
 ▶ 시키다
 도록
 집에 가게? / 가시게요?</t>
-  </si>
-  <si>
-    <t>Types of Verbs Pt.2 - Causative Verbs #1</t>
   </si>
   <si>
     <t>Causative verb 개념 Remind (나다 &amp; 내다 Remind)
@@ -1335,13 +1184,7 @@
   ▶ 아/어지다 VS 아/어뜨리다 (ex: 떨어지다 VS 떨어뜨리다)</t>
   </si>
   <si>
-    <t>Causative Verbs #2</t>
-  </si>
-  <si>
     <t>이리히기우추 suffix 룰</t>
-  </si>
-  <si>
-    <t>Quoting Form #1</t>
   </si>
   <si>
     <t>Plain form + 고 - Plain form Conjugation 다시 Recap
@@ -1352,14 +1195,8 @@
  - 약속하다, 믿다, 부르다</t>
   </si>
   <si>
-    <t>Quoting Form #2 - Short Quoting form</t>
-  </si>
-  <si>
     <t>대요, 냬요, 재요, 래요
 답니다, 냡니다, 잡니다, 랍니다</t>
-  </si>
-  <si>
-    <t>Quoting Form #3 - 이다 &amp; 한다</t>
   </si>
   <si>
     <t>한다고 보다 (라고 보다)
@@ -1369,57 +1206,30 @@
 다고 해도</t>
   </si>
   <si>
-    <t>Quoting Form #4 - 단다 &amp; 란다</t>
-  </si>
-  <si>
     <t>단다 &amp; 란다</t>
-  </si>
-  <si>
-    <t>Confirming Information</t>
   </si>
   <si>
     <t>Plain form + 며? - 한다며?
 Plain form + 면서요? - 한다면서요?</t>
   </si>
   <si>
-    <t>Quoting Form + Grammar form #1 는 것</t>
-  </si>
-  <si>
     <t>한다는 것 VS 하는 것
  - 할 거라는 것</t>
   </si>
   <si>
-    <t>Quoting Form + Grammar form #2 니까</t>
-  </si>
-  <si>
     <t>한다니까</t>
   </si>
   <si>
-    <t>I can't believe - 다니</t>
-  </si>
-  <si>
     <t>이렇게나 맛있다니!</t>
   </si>
   <si>
-    <t>Quoting Form + Grammar form #3 다기보다는</t>
-  </si>
-  <si>
     <t>그렇다기보다는</t>
   </si>
   <si>
-    <t>Quoting Form + Grammar form #4 다는 것이</t>
-  </si>
-  <si>
     <t>다는 것이 (노래를 튼다는 게 라디오를 틀어버렸네)</t>
   </si>
   <si>
-    <t>Quoting Form + Grammar form #5 다면</t>
-  </si>
-  <si>
     <t>그렇다(고 한다)면</t>
-  </si>
-  <si>
-    <t>Quoting Form + Grammar form #6 말이다</t>
   </si>
   <si>
     <t>단 말이다 / 냐는 말이다 / 자는 말이다 / 라는 말이다
@@ -1429,14 +1239,8 @@
  - 기에 말이지</t>
   </si>
   <si>
-    <t>Whether / If</t>
-  </si>
-  <si>
     <t>는지 &amp; ㄴ지
 ▶ 어쩐지, 왠지</t>
-  </si>
-  <si>
-    <t>Ever - (Whoever, Whatever, etc) &amp; Regardless</t>
   </si>
   <si>
     <t>Question word + 든지
@@ -1479,14 +1283,6 @@
 기에 길래</t>
   </si>
   <si>
-    <t>More Because #2</t>
-  </si>
-  <si>
-    <t>는 바람에
-고 해서
-~므로</t>
-  </si>
-  <si>
     <t>"테" - 테니까 &amp; 텐데</t>
   </si>
   <si>
@@ -1656,6 +1452,262 @@
   <si>
     <t>에게 / 한테 / 께 (Honorific Particle)
 에게서 / 한테서</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Why Korean avoids direct "you"; using titles, names, 오빠/언니/형/누나, when NOT to use 당신
+Honorific Family Titles
+ - 어머님, 아버님, 아드님, etc
+형, 오빠, 누나, 언니
+그쪽
+씨 vs 님
+성재는, 태훈이는
+성재야, 태훈아</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ji 레슨 주제 (brainstorm)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Course promo
+정식 레슨이 아니라 말그대로 Video Sales Letter
+ - overview of teaching philosophy
+ - 어떻게든 구매 전환이 많이 일어나게 하는 것이 목표</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>강의 기획 윤곽이 다 나오고 난 다음에 마지막으로 제작
+Course navigation, study tips, pacing
+ - 한글 배우고 나서 배워라라는 메시지
+  &gt; 각 레슨 별 worksheet 사용방법
+  &gt; Skool community에 질문하라는 안내
+  &gt; 효과적인 학습법 (Input process output)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">강의 기획 윤곽이 다 나오고 난 다음에 마지막으로 제작
+한국어의 단어 체계
+ - Sino-Korean vs Pure Korean vocabulary
+(선택하다 vs 고르다 type pairs)
+context-based learning
+ - 단어를 개별적으로 외우려고 들지 말고 full sentence로 공부해라
+  &gt; comprehensible input 소개
+  &gt; 그래야 context를 알 수 있다. 한국어는 high context 언어이다
+  &gt; 같은 단어도 어떤 맥락에서 쓰이느냐에 따라 뜻이 달라진다
+단어 공부법
+ - 마케팅 캠페인과 밀접한 연관이 있는 레슨 (marketing_plan.md 참조)
+  &gt; 무료자료 Lead (6000 most Common Korean words)
+  &gt; SRS (Spaced repetition System) 기반 Flashcard app Affiliate marketing으로 부가 수익 창출 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>End up doing</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>So that - 게 other usages &amp; 도록</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Verb → Noun #1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Easy &amp; hard to do</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Before &amp; After &amp; Since</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Start &amp; Stop doing</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decide to do</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>To hope</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기 + Markers (는, 도, 만)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adverbs #7 - Descriptive Verb → Adverb - 게</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Types of Verbs Pt.2 - Causative Verbs #1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Causative Verbs #2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form #1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form #2 - Short Quoting form</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form #3 - 이다 &amp; 한다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form #4 - 단다 &amp; 란다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Confirming Information</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form + Grammar form #1 는 것</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form + Grammar form #2 니까</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>I can't believe - 다니</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form + Grammar form #3 다기보다는</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form + Grammar form #4 다는 것이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form + Grammar form #5 다면</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quoting Form + Grammar form #6 말이다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Whether / If</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ever - (Whoever, Whatever, etc) &amp; Regardless</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block structure, design logic, vowel/consonant distinction
+ - ㅡ being the neutral vowel
+ - 외래어 spelling
+  &gt;Stress (1 syllable) → 스트레스 (4 syllables)
+발음 관련 Tip
+ - why ㄴ sounds like ㄷ &amp; why ㅁ sounds like ㅂ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>나/저, 우리/저희, 너, 얘/쟤/걔, 이 분/저 분/그 분
+ - Don't use 그 and 그녀
+의, contractions (나의→내, 저의→제, 너의→네→니);
+의 vs 네 possessive markers
+들 marker, when optional, 들 on non-nouns, 들 after phrases
+이것/저것/그것
+ - 이것은 OO예요.
+ - 이것은 → 이거는 → 이건 Contraction 설명</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Onomatopoeia &amp; Mimetic words + Verb</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plain, tense, aspirated consonants</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Types of consonants</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batchim &amp; Sound change rules</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sino-Korean numbers</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Native Korean numbers</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time &amp; Place #4 - Takes time, Has been time</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>는 바람에
+고 해서
+~므로
+지라</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>More Because #2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Politeness level에 대한 전체적인 개념 소개 및 용어 정리
+1. Speech level / Honorific / Humble speech
+Formal high/low
+Informal high/low
+Speech levels (polite 요, casual 반말, formal 니다)
+When to use which speech level &gt; Social, cultural dynamic 설명
+ - 언제 반말 쓸 수 있는지
+ - Difference between polite (요) VS formal (니다)
+ - Plain form 언제 쓰이는지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Descriptive Verbs &amp; Action Verbs
+아/어 conjugation rules, 하다→해요
+Important Verbs 하다
+ - 하다 Verb 설명 (Sino-Korean verbs all end in 하다)
+compound verbs &amp; connectors 간략히 소개만</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이다 VS 있다
+ - 에 있다 보여주면서 location marker "에" 간략히만 소개
+이다 conjugation 방법
+현재형
+ - (이)야
+ - 이에요 / 예요
+ - 입니다
+과거형
+- 이었 / 였어(요)
+- 이었/였습니다
+몇 살이예요? VS 나이가 어떻게 되세요?
+이름이 뭐예요? VS 성함이 어떻게 되세요?
+ - "되다"는 become이라는 뜻이지만 "어떻게 되세요? 를 통째로 외워라
+ - "되다"의 여러 사용법에 대해서는 추후 배우게 될 것
+제 이름은 OOO예요.
+ - 은/는 개념에 대해 간략히만 소개
+ - 은/는 받침유무에 따라 변경됨 설명</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요, 안녕히 가세요/계세요, 식사하셨어요, pattern recognition across speech levels
+감사합니다/고마워, 죄송합니다/미안해, 실례합니다/저기요
+반갑다 hidden meaning</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2505,19 +2557,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="4" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2858,282 +2910,282 @@
         <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="66.3" customHeight="1" thickTop="1" x14ac:dyDescent="0.7">
       <c r="A2" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="16">
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="E2" s="105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="99" x14ac:dyDescent="0.7">
+      <c r="A3" s="106" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" s="105" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A3" s="106" t="s">
-        <v>9</v>
       </c>
       <c r="B3" s="18">
         <v>1</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>11</v>
+        <v>343</v>
       </c>
       <c r="E3" s="105" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="264" customHeight="1" x14ac:dyDescent="0.7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="297" x14ac:dyDescent="0.7">
       <c r="A4" s="106" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="20">
         <v>2</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>13</v>
+        <v>344</v>
       </c>
       <c r="E4" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A5" s="85" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B5" s="17">
         <v>1</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>16</v>
+        <v>371</v>
       </c>
       <c r="E5" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A6" s="85" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B6" s="17">
         <v>2</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>18</v>
+        <v>374</v>
       </c>
       <c r="E6" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A7" s="85" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" s="17">
         <v>3</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>19</v>
+        <v>376</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E7" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A8" s="85" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B8" s="17">
         <v>4</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E8" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A9" s="85" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B9" s="17">
         <v>5</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E9" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="33.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A10" s="86" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B10" s="36">
         <v>6</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E10" s="105" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A11" s="87" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B11" s="38">
         <v>1</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E11" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A12" s="87" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B12" s="38">
         <v>2</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>31</v>
+        <v>377</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E12" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A13" s="87" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B13" s="38">
         <v>3</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>33</v>
+        <v>378</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E13" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A14" s="87" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B14" s="38">
         <v>4</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E14" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="87" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B15" s="38">
         <v>5</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E15" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A16" s="87" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B16" s="38">
         <v>6</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E16" s="105" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A17" s="88" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B17" s="41">
         <v>7</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E17" s="105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3144,13 +3196,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E18" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.7">
@@ -3161,13 +3213,13 @@
         <v>2</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>46</v>
+        <v>382</v>
       </c>
       <c r="E19" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3178,13 +3230,13 @@
         <v>3</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E20" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -3195,13 +3247,13 @@
         <v>4</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E21" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -3212,13 +3264,13 @@
         <v>5</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>52</v>
+        <v>383</v>
       </c>
       <c r="E22" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3229,13 +3281,13 @@
         <v>6</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E23" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3246,13 +3298,13 @@
         <v>7</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E24" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3263,13 +3315,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E25" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -3280,16 +3332,16 @@
         <v>9</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E26" s="108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="346.5" customHeight="1" x14ac:dyDescent="0.7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="363" x14ac:dyDescent="0.7">
       <c r="A27" s="89">
         <v>1</v>
       </c>
@@ -3297,13 +3349,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>62</v>
+        <v>384</v>
       </c>
       <c r="E27" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3314,16 +3366,16 @@
         <v>11</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D28" s="45" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E28" s="108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="148.5" x14ac:dyDescent="0.7">
       <c r="A29" s="89">
         <v>1</v>
       </c>
@@ -3331,13 +3383,13 @@
         <v>12</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>66</v>
+        <v>372</v>
       </c>
       <c r="E29" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="148.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3348,13 +3400,13 @@
         <v>13</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>68</v>
+        <v>340</v>
       </c>
       <c r="E30" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="148.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3365,13 +3417,13 @@
         <v>14</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D31" s="44" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E31" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -3382,13 +3434,13 @@
         <v>15</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>72</v>
+        <v>385</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3399,13 +3451,13 @@
         <v>16</v>
       </c>
       <c r="C33" s="44" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E33" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.7">
@@ -3416,13 +3468,13 @@
         <v>17</v>
       </c>
       <c r="C34" s="44" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E34" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="181.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3433,13 +3485,13 @@
         <v>18</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E35" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3450,13 +3502,13 @@
         <v>19</v>
       </c>
       <c r="C36" s="44" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E36" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3467,13 +3519,13 @@
         <v>20</v>
       </c>
       <c r="C37" s="44" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E37" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="33.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -3484,13 +3536,13 @@
         <v>21</v>
       </c>
       <c r="C38" s="44" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D38" s="44" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E38" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3501,13 +3553,13 @@
         <v>1</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D39" s="47" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E39" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3518,13 +3570,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E40" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="330" customHeight="1" x14ac:dyDescent="0.7">
@@ -3535,13 +3587,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E41" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3552,13 +3604,13 @@
         <v>4</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E42" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3569,13 +3621,13 @@
         <v>5</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E43" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3586,13 +3638,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E44" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3603,13 +3655,13 @@
         <v>7</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E45" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -3620,13 +3672,13 @@
         <v>8</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D46" s="51" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E46" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.7">
@@ -3637,13 +3689,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E47" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -3654,13 +3706,13 @@
         <v>10</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E48" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3671,13 +3723,13 @@
         <v>1</v>
       </c>
       <c r="C49" s="53" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D49" s="53" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E49" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -3688,13 +3740,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="55" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D50" s="55" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="E50" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -3705,13 +3757,13 @@
         <v>3</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D51" s="55" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E51" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -3722,13 +3774,13 @@
         <v>4</v>
       </c>
       <c r="C52" s="56" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D52" s="56" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E52" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3739,13 +3791,13 @@
         <v>5</v>
       </c>
       <c r="C53" s="55" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D53" s="55" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E53" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3756,13 +3808,13 @@
         <v>6</v>
       </c>
       <c r="C54" s="55" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E54" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3773,13 +3825,13 @@
         <v>7</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E55" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -3790,13 +3842,13 @@
         <v>8</v>
       </c>
       <c r="C56" s="55" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D56" s="55" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E56" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -3807,13 +3859,13 @@
         <v>9</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="D57" s="55" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E57" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -3824,13 +3876,13 @@
         <v>10</v>
       </c>
       <c r="C58" s="55" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D58" s="55" t="s">
-        <v>385</v>
+        <v>339</v>
       </c>
       <c r="E58" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3841,13 +3893,13 @@
         <v>11</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="E59" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3858,13 +3910,13 @@
         <v>12</v>
       </c>
       <c r="C60" s="55" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D60" s="55" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E60" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3875,13 +3927,13 @@
         <v>13</v>
       </c>
       <c r="C61" s="55" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D61" s="55" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E61" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="231.3" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -3892,13 +3944,13 @@
         <v>14</v>
       </c>
       <c r="C62" s="55" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D62" s="56" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E62" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3909,13 +3961,13 @@
         <v>1</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="E63" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -3926,13 +3978,13 @@
         <v>2</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E64" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -3943,13 +3995,13 @@
         <v>3</v>
       </c>
       <c r="C65" s="59" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D65" s="59" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E65" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="181.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -3960,13 +4012,13 @@
         <v>4</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="E66" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -3977,13 +4029,13 @@
         <v>5</v>
       </c>
       <c r="C67" s="63" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D67" s="63" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="E67" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -3994,13 +4046,13 @@
         <v>6</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="E68" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4011,13 +4063,13 @@
         <v>7</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="E69" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="264" customHeight="1" x14ac:dyDescent="0.7">
@@ -4028,13 +4080,13 @@
         <v>8</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="E70" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -4045,13 +4097,13 @@
         <v>9</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="E71" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.7">
@@ -4062,13 +4114,13 @@
         <v>10</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="E72" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -4079,13 +4131,13 @@
         <v>11</v>
       </c>
       <c r="C73" s="67" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D73" s="67" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="E73" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4096,13 +4148,13 @@
         <v>12</v>
       </c>
       <c r="C74" s="61" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="D74" s="61" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="E74" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.7">
@@ -4113,13 +4165,13 @@
         <v>13</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E75" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="198.3" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -4130,13 +4182,13 @@
         <v>14</v>
       </c>
       <c r="C76" s="69" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="D76" s="69" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E76" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -4147,13 +4199,13 @@
         <v>1</v>
       </c>
       <c r="C77" s="71" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D77" s="71" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E77" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.7">
@@ -4164,13 +4216,13 @@
         <v>2</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E78" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.7">
@@ -4181,13 +4233,13 @@
         <v>3</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E79" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.7">
@@ -4198,13 +4250,13 @@
         <v>4</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="E80" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4215,13 +4267,13 @@
         <v>5</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="E81" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -4232,13 +4284,13 @@
         <v>6</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>170</v>
+        <v>373</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="E82" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="198" customHeight="1" x14ac:dyDescent="0.7">
@@ -4249,13 +4301,13 @@
         <v>7</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E83" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4266,13 +4318,13 @@
         <v>8</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="E84" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="148.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4283,13 +4335,13 @@
         <v>9</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E85" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -4300,13 +4352,13 @@
         <v>10</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="E86" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -4317,13 +4369,13 @@
         <v>11</v>
       </c>
       <c r="C87" s="73" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D87" s="73" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="E87" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="132.30000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -4334,13 +4386,13 @@
         <v>12</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="E88" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="313.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4351,13 +4403,13 @@
         <v>1</v>
       </c>
       <c r="C89" s="75" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="D89" s="75" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="E89" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4368,13 +4420,13 @@
         <v>2</v>
       </c>
       <c r="C90" s="77" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="D90" s="78" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="E90" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4385,13 +4437,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="77" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D91" s="77" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="E91" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -4402,13 +4454,13 @@
         <v>4</v>
       </c>
       <c r="C92" s="77" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="D92" s="77" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="E92" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -4419,13 +4471,13 @@
         <v>5</v>
       </c>
       <c r="C93" s="77" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="D93" s="77" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="E93" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4436,13 +4488,13 @@
         <v>6</v>
       </c>
       <c r="C94" s="77" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="D94" s="77" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E94" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -4453,13 +4505,13 @@
         <v>7</v>
       </c>
       <c r="C95" s="77" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="D95" s="77" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="E95" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4470,13 +4522,13 @@
         <v>8</v>
       </c>
       <c r="C96" s="77" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D96" s="77" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="E96" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -4487,13 +4539,13 @@
         <v>9</v>
       </c>
       <c r="C97" s="77" t="s">
-        <v>200</v>
+        <v>379</v>
       </c>
       <c r="D97" s="77" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="E97" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4504,13 +4556,13 @@
         <v>10</v>
       </c>
       <c r="C98" s="77" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="D98" s="77" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E98" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.7">
@@ -4521,13 +4573,13 @@
         <v>11</v>
       </c>
       <c r="C99" s="77" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="D99" s="78" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="E99" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="231.3" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -4538,13 +4590,13 @@
         <v>12</v>
       </c>
       <c r="C100" s="80" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="D100" s="80" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="E100" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -4555,13 +4607,13 @@
         <v>1</v>
       </c>
       <c r="C101" s="33" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="D101" s="33" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="E101" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4572,13 +4624,13 @@
         <v>2</v>
       </c>
       <c r="C102" s="33" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="D102" s="33" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="E102" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.7">
@@ -4589,13 +4641,13 @@
         <v>3</v>
       </c>
       <c r="C103" s="33" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D103" s="33" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="E103" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4606,13 +4658,13 @@
         <v>4</v>
       </c>
       <c r="C104" s="33" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="D104" s="33" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="E104" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4623,13 +4675,13 @@
         <v>5</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="E105" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4640,13 +4692,13 @@
         <v>6</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="E106" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.7">
@@ -4657,13 +4709,13 @@
         <v>7</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="E107" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4674,13 +4726,13 @@
         <v>8</v>
       </c>
       <c r="C108" s="33" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="E108" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="148.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4691,13 +4743,13 @@
         <v>9</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="E109" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4708,13 +4760,13 @@
         <v>10</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="E110" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -4725,13 +4777,13 @@
         <v>11</v>
       </c>
       <c r="C111" s="33" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="D111" s="33" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E111" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.7">
@@ -4742,13 +4794,13 @@
         <v>12</v>
       </c>
       <c r="C112" s="33" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="D112" s="33" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="E112" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4759,13 +4811,13 @@
         <v>13</v>
       </c>
       <c r="C113" s="35" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D113" s="35" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="E113" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -4776,13 +4828,13 @@
         <v>14</v>
       </c>
       <c r="C114" s="33" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="D114" s="33" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="E114" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.7">
@@ -4793,13 +4845,13 @@
         <v>15</v>
       </c>
       <c r="C115" s="33" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="D115" s="33" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="E115" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.7">
@@ -4810,13 +4862,13 @@
         <v>16</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="D116" s="19" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="E116" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4827,13 +4879,13 @@
         <v>17</v>
       </c>
       <c r="C117" s="35" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D117" s="35" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="E117" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4844,13 +4896,13 @@
         <v>18</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D118" s="35" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="E118" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.7">
@@ -4861,13 +4913,13 @@
         <v>19</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="E119" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4878,13 +4930,13 @@
         <v>20</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D120" s="19" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="E120" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.7">
@@ -4895,13 +4947,13 @@
         <v>1</v>
       </c>
       <c r="C121" s="55" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="D121" s="56" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E121" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -4912,13 +4964,13 @@
         <v>2</v>
       </c>
       <c r="C122" s="55" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="D122" s="55" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="E122" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -4929,13 +4981,13 @@
         <v>3</v>
       </c>
       <c r="C123" s="55" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="D123" s="55" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="E123" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4946,13 +4998,13 @@
         <v>4</v>
       </c>
       <c r="C124" s="55" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D124" s="55" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E124" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4963,13 +5015,13 @@
         <v>5</v>
       </c>
       <c r="C125" s="55" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="D125" s="55" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="E125" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.7">
@@ -4980,13 +5032,13 @@
         <v>6</v>
       </c>
       <c r="C126" s="55" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D126" s="56" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="E126" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -4997,13 +5049,13 @@
         <v>7</v>
       </c>
       <c r="C127" s="55" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="D127" s="55" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="E127" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.7">
@@ -5014,13 +5066,13 @@
         <v>8</v>
       </c>
       <c r="C128" s="55" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="D128" s="55" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="E128" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5031,13 +5083,13 @@
         <v>9</v>
       </c>
       <c r="C129" s="55" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="D129" s="55" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="E129" s="108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5048,13 +5100,13 @@
         <v>10</v>
       </c>
       <c r="C130" s="55" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="D130" s="55" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="E130" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -5065,13 +5117,13 @@
         <v>11</v>
       </c>
       <c r="C131" s="55" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="D131" s="55" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="E131" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.7">
@@ -5082,13 +5134,13 @@
         <v>12</v>
       </c>
       <c r="C132" s="55" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="D132" s="56" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="E132" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -5099,13 +5151,13 @@
         <v>1</v>
       </c>
       <c r="C133" s="49" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
       <c r="D133" s="49" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="E133" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5116,13 +5168,13 @@
         <v>2</v>
       </c>
       <c r="C134" s="49" t="s">
-        <v>274</v>
+        <v>348</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="E134" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5133,13 +5185,13 @@
         <v>3</v>
       </c>
       <c r="C135" s="49" t="s">
-        <v>276</v>
+        <v>349</v>
       </c>
       <c r="D135" s="49" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="E135" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.7">
@@ -5150,13 +5202,13 @@
         <v>4</v>
       </c>
       <c r="C136" s="49" t="s">
-        <v>278</v>
+        <v>350</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="E136" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5167,13 +5219,13 @@
         <v>5</v>
       </c>
       <c r="C137" s="49" t="s">
-        <v>280</v>
+        <v>351</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="E137" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5184,13 +5236,13 @@
         <v>6</v>
       </c>
       <c r="C138" s="49" t="s">
-        <v>282</v>
+        <v>352</v>
       </c>
       <c r="D138" s="51" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="E138" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5201,13 +5253,13 @@
         <v>7</v>
       </c>
       <c r="C139" s="49" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="D139" s="49" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="E139" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5218,13 +5270,13 @@
         <v>8</v>
       </c>
       <c r="C140" s="49" t="s">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="D140" s="49" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="E140" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5235,13 +5287,13 @@
         <v>9</v>
       </c>
       <c r="C141" s="49" t="s">
-        <v>288</v>
+        <v>345</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="E141" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5252,13 +5304,13 @@
         <v>10</v>
       </c>
       <c r="C142" s="49" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="D142" s="49" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="E142" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -5269,13 +5321,13 @@
         <v>11</v>
       </c>
       <c r="C143" s="49" t="s">
-        <v>292</v>
+        <v>355</v>
       </c>
       <c r="D143" s="49" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="E143" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.7">
@@ -5286,13 +5338,13 @@
         <v>12</v>
       </c>
       <c r="C144" s="49" t="s">
-        <v>294</v>
+        <v>356</v>
       </c>
       <c r="D144" s="51" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="E144" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5303,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>296</v>
+        <v>357</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="E145" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5320,13 +5372,13 @@
         <v>2</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>299</v>
+        <v>267</v>
       </c>
       <c r="E146" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5337,13 +5389,13 @@
         <v>3</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="E147" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.7">
@@ -5354,13 +5406,13 @@
         <v>4</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="E148" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5371,13 +5423,13 @@
         <v>5</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="E149" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5388,13 +5440,13 @@
         <v>6</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="E150" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.7">
@@ -5405,13 +5457,13 @@
         <v>7</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>308</v>
+        <v>363</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="E151" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.7">
@@ -5422,13 +5474,13 @@
         <v>8</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="E152" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.7">
@@ -5439,13 +5491,13 @@
         <v>9</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>313</v>
+        <v>274</v>
       </c>
       <c r="E153" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.7">
@@ -5456,13 +5508,13 @@
         <v>10</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>314</v>
+        <v>366</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="E154" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.7">
@@ -5473,13 +5525,13 @@
         <v>11</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="E155" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
@@ -5490,13 +5542,13 @@
         <v>12</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>318</v>
+        <v>368</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="E156" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5507,13 +5559,13 @@
         <v>13</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>320</v>
+        <v>369</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="E157" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5524,13 +5576,13 @@
         <v>14</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>323</v>
+        <v>279</v>
       </c>
       <c r="E158" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5541,13 +5593,13 @@
         <v>1</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>325</v>
+        <v>281</v>
       </c>
       <c r="E159" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
@@ -5558,13 +5610,13 @@
         <v>2</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>327</v>
+        <v>283</v>
       </c>
       <c r="E160" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5575,13 +5627,13 @@
         <v>3</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="E161" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5592,16 +5644,16 @@
         <v>4</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="E162" s="108" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="66" x14ac:dyDescent="0.7">
       <c r="A163" s="109">
         <v>11</v>
       </c>
@@ -5609,13 +5661,13 @@
         <v>5</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>332</v>
+        <v>381</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>333</v>
+        <v>380</v>
       </c>
       <c r="E163" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5626,13 +5678,13 @@
         <v>6</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="E164" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.7">
@@ -5643,13 +5695,13 @@
         <v>7</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="E165" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -5660,13 +5712,13 @@
         <v>8</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>338</v>
+        <v>292</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>339</v>
+        <v>293</v>
       </c>
       <c r="E166" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.7">
@@ -5677,13 +5729,13 @@
         <v>9</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>340</v>
+        <v>294</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>341</v>
+        <v>295</v>
       </c>
       <c r="E167" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -5694,13 +5746,13 @@
         <v>10</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>342</v>
+        <v>296</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>343</v>
+        <v>297</v>
       </c>
       <c r="E168" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.7">
@@ -5711,13 +5763,13 @@
         <v>11</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>344</v>
+        <v>298</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="E169" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5728,13 +5780,13 @@
         <v>12</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>347</v>
+        <v>301</v>
       </c>
       <c r="E170" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.7">
@@ -5745,13 +5797,13 @@
         <v>13</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="D171" s="82" t="s">
-        <v>349</v>
+        <v>303</v>
       </c>
       <c r="E171" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.7">
@@ -5762,13 +5814,13 @@
         <v>14</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>350</v>
+        <v>304</v>
       </c>
       <c r="D172" s="73" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="E172" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.7">
@@ -5779,13 +5831,13 @@
         <v>15</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>352</v>
+        <v>306</v>
       </c>
       <c r="D173" s="73" t="s">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="E173" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.7">
@@ -5796,13 +5848,13 @@
         <v>16</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="D174" s="73" t="s">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="E174" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
@@ -5813,13 +5865,13 @@
         <v>17</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>355</v>
+        <v>309</v>
       </c>
       <c r="D175" s="73" t="s">
-        <v>356</v>
+        <v>310</v>
       </c>
       <c r="E175" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.7">
@@ -5830,13 +5882,13 @@
         <v>18</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="D176" s="73" t="s">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="E176" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.7">
@@ -5847,13 +5899,13 @@
         <v>19</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="D177" s="73" t="s">
-        <v>359</v>
+        <v>313</v>
       </c>
       <c r="E177" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.7">
@@ -5864,13 +5916,13 @@
         <v>20</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="D178" s="73" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
       <c r="E178" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
@@ -5881,13 +5933,13 @@
         <v>21</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="D179" s="73" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
       <c r="E179" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.7">
@@ -5898,11 +5950,11 @@
         <v>22</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.7">
@@ -5913,11 +5965,11 @@
         <v>1</v>
       </c>
       <c r="C181" s="84" t="s">
-        <v>365</v>
+        <v>319</v>
       </c>
       <c r="D181" s="9"/>
       <c r="E181" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.7">
@@ -5928,11 +5980,11 @@
         <v>2</v>
       </c>
       <c r="C182" s="84" t="s">
-        <v>366</v>
+        <v>320</v>
       </c>
       <c r="D182" s="9"/>
       <c r="E182" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.7">
@@ -5943,11 +5995,11 @@
         <v>3</v>
       </c>
       <c r="C183" s="84" t="s">
-        <v>367</v>
+        <v>321</v>
       </c>
       <c r="D183" s="9"/>
       <c r="E183" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.7">
@@ -5958,11 +6010,11 @@
         <v>4</v>
       </c>
       <c r="C184" s="84" t="s">
-        <v>368</v>
+        <v>322</v>
       </c>
       <c r="D184" s="9"/>
       <c r="E184" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.7">
@@ -5973,11 +6025,11 @@
         <v>5</v>
       </c>
       <c r="C185" s="84" t="s">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="D185" s="9"/>
       <c r="E185" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.7">
@@ -5988,11 +6040,11 @@
         <v>6</v>
       </c>
       <c r="C186" s="84" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="D186" s="9"/>
       <c r="E186" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.7">
@@ -6003,11 +6055,11 @@
         <v>7</v>
       </c>
       <c r="C187" s="84" t="s">
-        <v>371</v>
+        <v>325</v>
       </c>
       <c r="D187" s="9"/>
       <c r="E187" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.7">
@@ -6018,11 +6070,11 @@
         <v>8</v>
       </c>
       <c r="C188" s="84" t="s">
-        <v>372</v>
+        <v>326</v>
       </c>
       <c r="D188" s="9"/>
       <c r="E188" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.7">
@@ -6033,11 +6085,11 @@
         <v>9</v>
       </c>
       <c r="C189" s="84" t="s">
-        <v>373</v>
+        <v>327</v>
       </c>
       <c r="D189" s="9"/>
       <c r="E189" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.7">
@@ -6048,11 +6100,11 @@
         <v>10</v>
       </c>
       <c r="C190" s="84" t="s">
-        <v>374</v>
+        <v>328</v>
       </c>
       <c r="D190" s="9"/>
       <c r="E190" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.7">
@@ -6063,11 +6115,11 @@
         <v>11</v>
       </c>
       <c r="C191" s="84" t="s">
-        <v>375</v>
+        <v>329</v>
       </c>
       <c r="D191" s="9"/>
       <c r="E191" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.7">
@@ -6078,11 +6130,11 @@
         <v>12</v>
       </c>
       <c r="C192" s="84" t="s">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="D192" s="9"/>
       <c r="E192" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.7">
@@ -6093,11 +6145,11 @@
         <v>13</v>
       </c>
       <c r="C193" s="84" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="D193" s="9"/>
       <c r="E193" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.7">
@@ -6108,11 +6160,11 @@
         <v>14</v>
       </c>
       <c r="C194" s="84" t="s">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="D194" s="9"/>
       <c r="E194" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
@@ -6123,13 +6175,13 @@
         <v>15</v>
       </c>
       <c r="C195" s="84" t="s">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>380</v>
+        <v>334</v>
       </c>
       <c r="E195" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.7">
@@ -6140,13 +6192,13 @@
         <v>16</v>
       </c>
       <c r="C196" s="84" t="s">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="E196" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.7">
@@ -6157,13 +6209,13 @@
         <v>17</v>
       </c>
       <c r="C197" s="84" t="s">
-        <v>383</v>
+        <v>337</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="E197" s="108" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.7">
@@ -9031,10 +9083,389 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F213A4A-B708-49BF-9523-D0135F685F07}">
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.7"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="46.94921875" customWidth="1"/>
+    <col min="4" max="4" width="61.44921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+      <c r="A2" s="107">
+        <v>1</v>
+      </c>
+      <c r="B2" s="43">
+        <v>1</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="165" x14ac:dyDescent="0.7">
+      <c r="A3" s="89">
+        <v>1</v>
+      </c>
+      <c r="B3" s="43">
+        <v>2</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="E3" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+      <c r="A4" s="89">
+        <v>1</v>
+      </c>
+      <c r="B4" s="43">
+        <v>3</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="66" x14ac:dyDescent="0.7">
+      <c r="A5" s="89">
+        <v>1</v>
+      </c>
+      <c r="B5" s="43">
+        <v>4</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="346.5" x14ac:dyDescent="0.7">
+      <c r="A6" s="89">
+        <v>1</v>
+      </c>
+      <c r="B6" s="43">
+        <v>10</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>384</v>
+      </c>
+      <c r="E6" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+      <c r="A7" s="89">
+        <v>1</v>
+      </c>
+      <c r="B7" s="43">
+        <v>11</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="148.5" x14ac:dyDescent="0.7">
+      <c r="A8" s="89">
+        <v>1</v>
+      </c>
+      <c r="B8" s="43">
+        <v>12</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="E8" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="132" x14ac:dyDescent="0.7">
+      <c r="A9" s="89">
+        <v>1</v>
+      </c>
+      <c r="B9" s="43">
+        <v>5</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>383</v>
+      </c>
+      <c r="E9" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="A10" s="89">
+        <v>1</v>
+      </c>
+      <c r="B10" s="43">
+        <v>6</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+      <c r="A11" s="89">
+        <v>1</v>
+      </c>
+      <c r="B11" s="43">
+        <v>7</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="A12" s="89">
+        <v>1</v>
+      </c>
+      <c r="B12" s="43">
+        <v>8</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="132" x14ac:dyDescent="0.7">
+      <c r="A13" s="89">
+        <v>1</v>
+      </c>
+      <c r="B13" s="43">
+        <v>9</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="148.5" x14ac:dyDescent="0.7">
+      <c r="A14" s="89">
+        <v>1</v>
+      </c>
+      <c r="B14" s="43">
+        <v>13</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="E14" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="148.5" x14ac:dyDescent="0.7">
+      <c r="A15" s="89">
+        <v>1</v>
+      </c>
+      <c r="B15" s="43">
+        <v>14</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="66" x14ac:dyDescent="0.7">
+      <c r="A16" s="89">
+        <v>1</v>
+      </c>
+      <c r="B16" s="43">
+        <v>15</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>385</v>
+      </c>
+      <c r="E16" s="108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="A17" s="89">
+        <v>1</v>
+      </c>
+      <c r="B17" s="43">
+        <v>16</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="165" x14ac:dyDescent="0.7">
+      <c r="A18" s="89">
+        <v>1</v>
+      </c>
+      <c r="B18" s="43">
+        <v>17</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="181.5" x14ac:dyDescent="0.7">
+      <c r="A19" s="89">
+        <v>1</v>
+      </c>
+      <c r="B19" s="43">
+        <v>18</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="A20" s="89">
+        <v>1</v>
+      </c>
+      <c r="B20" s="43">
+        <v>19</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="A21" s="89">
+        <v>1</v>
+      </c>
+      <c r="B21" s="43">
+        <v>20</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+      <c r="A22" s="89">
+        <v>1</v>
+      </c>
+      <c r="B22" s="43">
+        <v>21</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/02_product/02_course_creation/00_curriculum_and_index/Korean Course Curriculum Map_Final_V7.xlsx
+++ b/02_product/02_course_creation/00_curriculum_and_index/Korean Course Curriculum Map_Final_V7.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vault\Koreanwithji_vault\02_product\02_course_creation\00_curriculum_and_index\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vault\koreanwithji_vault\02_product\02_course_creation\00_curriculum_and_index\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D587773-900F-462E-8555-4A698A8B6DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9BCBFB-F354-4BC6-9AC7-A8B44EF5F209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="7500" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curriculum Map" sheetId="1" r:id="rId1"/>
     <sheet name="레벨1순서update" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Curriculum Map'!$A$1:$E$197</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1715,7 +1718,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2888,18 +2891,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E930"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="9.84765625" style="104" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="104" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.09765625" style="6" customWidth="1"/>
-    <col min="5" max="6" width="8.59765625" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.59765625" style="4"/>
+    <col min="4" max="4" width="59.08203125" style="6" customWidth="1"/>
+    <col min="5" max="6" width="8.58203125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.58203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" ht="33.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="33.25" customHeight="1" thickBot="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2916,7 +2920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="66.3" customHeight="1" thickTop="1" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:5" ht="66.25" customHeight="1" thickTop="1">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -2933,7 +2937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="99" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:5" ht="102">
       <c r="A3" s="106" t="s">
         <v>7</v>
       </c>
@@ -2950,7 +2954,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="297" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:5" ht="289">
       <c r="A4" s="106" t="s">
         <v>7</v>
       </c>
@@ -2967,7 +2971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:5" ht="115.5" customHeight="1">
       <c r="A5" s="85" t="s">
         <v>10</v>
       </c>
@@ -2984,7 +2988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:5">
       <c r="A6" s="85" t="s">
         <v>10</v>
       </c>
@@ -3001,7 +3005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:5" ht="49.5" customHeight="1">
       <c r="A7" s="85" t="s">
         <v>10</v>
       </c>
@@ -3018,7 +3022,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:5">
       <c r="A8" s="85" t="s">
         <v>10</v>
       </c>
@@ -3035,7 +3039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:5" ht="115.5" customHeight="1">
       <c r="A9" s="85" t="s">
         <v>10</v>
       </c>
@@ -3052,7 +3056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="33.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:5" ht="33.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A10" s="86" t="s">
         <v>10</v>
       </c>
@@ -3069,7 +3073,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="11" spans="1:5">
       <c r="A11" s="87" t="s">
         <v>20</v>
       </c>
@@ -3086,7 +3090,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="12" spans="1:5">
       <c r="A12" s="87" t="s">
         <v>20</v>
       </c>
@@ -3103,7 +3107,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="13" spans="1:5">
       <c r="A13" s="87" t="s">
         <v>20</v>
       </c>
@@ -3120,7 +3124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="14" spans="1:5" ht="49.5" customHeight="1">
       <c r="A14" s="87" t="s">
         <v>20</v>
       </c>
@@ -3137,7 +3141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:5" ht="49.5" customHeight="1">
       <c r="A15" s="87" t="s">
         <v>20</v>
       </c>
@@ -3154,7 +3158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:5" hidden="1">
       <c r="A16" s="87" t="s">
         <v>20</v>
       </c>
@@ -3171,7 +3175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="17" spans="1:5">
       <c r="A17" s="88" t="s">
         <v>20</v>
       </c>
@@ -3188,7 +3192,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="18" spans="1:5" ht="33" customHeight="1">
       <c r="A18" s="107">
         <v>1</v>
       </c>
@@ -3205,7 +3209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="19" spans="1:5" ht="165" customHeight="1">
       <c r="A19" s="89">
         <v>1</v>
       </c>
@@ -3222,7 +3226,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="20" spans="1:5" ht="33" customHeight="1">
       <c r="A20" s="89">
         <v>1</v>
       </c>
@@ -3239,7 +3243,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="21" spans="1:5" ht="66" customHeight="1">
       <c r="A21" s="89">
         <v>1</v>
       </c>
@@ -3256,7 +3260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="22" spans="1:5" ht="132" customHeight="1">
       <c r="A22" s="89">
         <v>1</v>
       </c>
@@ -3273,7 +3277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="23" spans="1:5" ht="49.5" customHeight="1">
       <c r="A23" s="89">
         <v>1</v>
       </c>
@@ -3290,7 +3294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="24" spans="1:5" ht="33" customHeight="1">
       <c r="A24" s="89">
         <v>1</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="25" spans="1:5" ht="82.5" customHeight="1">
       <c r="A25" s="89">
         <v>1</v>
       </c>
@@ -3324,7 +3328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="26" spans="1:5" ht="132" customHeight="1">
       <c r="A26" s="89">
         <v>1</v>
       </c>
@@ -3341,7 +3345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="363" x14ac:dyDescent="0.7">
+    <row r="27" spans="1:5" ht="374">
       <c r="A27" s="89">
         <v>1</v>
       </c>
@@ -3358,7 +3362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="28" spans="1:5" ht="33" customHeight="1">
       <c r="A28" s="89">
         <v>1</v>
       </c>
@@ -3375,7 +3379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="148.5" x14ac:dyDescent="0.7">
+    <row r="29" spans="1:5" ht="153">
       <c r="A29" s="89">
         <v>1</v>
       </c>
@@ -3392,7 +3396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="148.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="30" spans="1:5" ht="148.5" customHeight="1">
       <c r="A30" s="89">
         <v>1</v>
       </c>
@@ -3409,7 +3413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="148.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="31" spans="1:5" ht="148.5" customHeight="1">
       <c r="A31" s="89">
         <v>1</v>
       </c>
@@ -3426,7 +3430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="32" spans="1:5" ht="66" hidden="1" customHeight="1">
       <c r="A32" s="89">
         <v>1</v>
       </c>
@@ -3443,7 +3447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="33" spans="1:5" ht="115.5" customHeight="1">
       <c r="A33" s="89">
         <v>1</v>
       </c>
@@ -3460,7 +3464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="34" spans="1:5" ht="165" customHeight="1">
       <c r="A34" s="89">
         <v>1</v>
       </c>
@@ -3477,7 +3481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="181.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="35" spans="1:5" ht="181.5" hidden="1" customHeight="1">
       <c r="A35" s="89">
         <v>1</v>
       </c>
@@ -3494,7 +3498,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="36" spans="1:5" ht="115.5" customHeight="1">
       <c r="A36" s="89">
         <v>1</v>
       </c>
@@ -3511,7 +3515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="37" spans="1:5" ht="49.5" customHeight="1" thickBot="1">
       <c r="A37" s="89">
         <v>1</v>
       </c>
@@ -3528,7 +3532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="33.299999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:5" ht="33.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A38" s="89">
         <v>1</v>
       </c>
@@ -3545,7 +3549,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="39" spans="1:5" ht="33" customHeight="1">
       <c r="A39" s="90">
         <v>2</v>
       </c>
@@ -3562,7 +3566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="40" spans="1:5" ht="82.5" customHeight="1">
       <c r="A40" s="91">
         <v>2</v>
       </c>
@@ -3579,7 +3583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="330" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="41" spans="1:5" ht="330" customHeight="1">
       <c r="A41" s="91">
         <v>2</v>
       </c>
@@ -3596,7 +3600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="42" spans="1:5" ht="33" customHeight="1">
       <c r="A42" s="91">
         <v>2</v>
       </c>
@@ -3613,7 +3617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="43" spans="1:5" ht="33" customHeight="1">
       <c r="A43" s="91">
         <v>2</v>
       </c>
@@ -3630,7 +3634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="44" spans="1:5" ht="33" customHeight="1">
       <c r="A44" s="91">
         <v>2</v>
       </c>
@@ -3647,7 +3651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="45" spans="1:5" ht="82.5" customHeight="1">
       <c r="A45" s="91">
         <v>2</v>
       </c>
@@ -3664,7 +3668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="46" spans="1:5" ht="99" hidden="1" customHeight="1">
       <c r="A46" s="91">
         <v>2</v>
       </c>
@@ -3681,7 +3685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="47" spans="1:5">
       <c r="A47" s="91">
         <v>2</v>
       </c>
@@ -3698,7 +3702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:5" ht="16.75" customHeight="1" thickBot="1">
       <c r="A48" s="91">
         <v>2</v>
       </c>
@@ -3715,7 +3719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="49" spans="1:5" ht="33" customHeight="1">
       <c r="A49" s="92">
         <v>3</v>
       </c>
@@ -3732,7 +3736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="50" spans="1:5" ht="132" customHeight="1">
       <c r="A50" s="93">
         <v>3</v>
       </c>
@@ -3749,7 +3753,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="51" spans="1:5" ht="132" hidden="1" customHeight="1">
       <c r="A51" s="93">
         <v>3</v>
       </c>
@@ -3766,7 +3770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="52" spans="1:5" ht="99" hidden="1" customHeight="1">
       <c r="A52" s="93">
         <v>3</v>
       </c>
@@ -3783,7 +3787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="53" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A53" s="93">
         <v>3</v>
       </c>
@@ -3800,7 +3804,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="54" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A54" s="93">
         <v>3</v>
       </c>
@@ -3817,7 +3821,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="55" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A55" s="93">
         <v>3</v>
       </c>
@@ -3834,7 +3838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="56" spans="1:5" ht="66" customHeight="1">
       <c r="A56" s="93">
         <v>3</v>
       </c>
@@ -3851,7 +3855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="57" spans="1:5" ht="99" customHeight="1">
       <c r="A57" s="93">
         <v>3</v>
       </c>
@@ -3868,7 +3872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="58" spans="1:5" ht="66" customHeight="1">
       <c r="A58" s="93">
         <v>3</v>
       </c>
@@ -3885,7 +3889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="59" spans="1:5" ht="33" customHeight="1">
       <c r="A59" s="93">
         <v>3</v>
       </c>
@@ -3902,7 +3906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="60" spans="1:5" ht="82.5" customHeight="1">
       <c r="A60" s="93">
         <v>3</v>
       </c>
@@ -3919,7 +3923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="61" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A61" s="93">
         <v>3</v>
       </c>
@@ -3936,7 +3940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="231.3" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:5" ht="231.25" customHeight="1" thickBot="1">
       <c r="A62" s="93">
         <v>3</v>
       </c>
@@ -3953,7 +3957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="63" spans="1:5" ht="49.5" customHeight="1">
       <c r="A63" s="21">
         <v>4</v>
       </c>
@@ -3970,7 +3974,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="64" spans="1:5" ht="99" customHeight="1">
       <c r="A64" s="24">
         <v>4</v>
       </c>
@@ -3987,7 +3991,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="65" spans="1:5" ht="99" customHeight="1">
       <c r="A65" s="24">
         <v>4</v>
       </c>
@@ -4004,7 +4008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="181.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="66" spans="1:5" ht="181.5" customHeight="1">
       <c r="A66" s="24">
         <v>4</v>
       </c>
@@ -4021,7 +4025,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="67" spans="1:5" ht="66" customHeight="1">
       <c r="A67" s="24">
         <v>4</v>
       </c>
@@ -4038,7 +4042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="68" spans="1:5" ht="33" customHeight="1">
       <c r="A68" s="24">
         <v>4</v>
       </c>
@@ -4055,7 +4059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="69" spans="1:5" ht="115.5" hidden="1" customHeight="1">
       <c r="A69" s="25">
         <v>4</v>
       </c>
@@ -4072,7 +4076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="264" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="70" spans="1:5" ht="264" customHeight="1">
       <c r="A70" s="24">
         <v>4</v>
       </c>
@@ -4089,7 +4093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="71" spans="1:5" ht="99" hidden="1" customHeight="1">
       <c r="A71" s="24">
         <v>4</v>
       </c>
@@ -4106,7 +4110,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="72" spans="1:5">
       <c r="A72" s="24">
         <v>4</v>
       </c>
@@ -4123,7 +4127,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="73" spans="1:5" ht="66" hidden="1" customHeight="1">
       <c r="A73" s="24">
         <v>4</v>
       </c>
@@ -4140,7 +4144,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="74" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A74" s="24">
         <v>4</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="75" spans="1:5" hidden="1">
       <c r="A75" s="24">
         <v>4</v>
       </c>
@@ -4174,7 +4178,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="198.3" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:5" ht="198.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A76" s="30">
         <v>4</v>
       </c>
@@ -4191,7 +4195,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="77" spans="1:5" ht="66" hidden="1" customHeight="1">
       <c r="A77" s="94">
         <v>5</v>
       </c>
@@ -4208,7 +4212,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="78" spans="1:5" hidden="1">
       <c r="A78" s="95">
         <v>5</v>
       </c>
@@ -4225,7 +4229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="79" spans="1:5" hidden="1">
       <c r="A79" s="95">
         <v>5</v>
       </c>
@@ -4242,7 +4246,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="80" spans="1:5" hidden="1">
       <c r="A80" s="95">
         <v>5</v>
       </c>
@@ -4259,7 +4263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="81" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A81" s="95">
         <v>5</v>
       </c>
@@ -4276,7 +4280,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="82" spans="1:5" ht="132" hidden="1" customHeight="1">
       <c r="A82" s="95">
         <v>5</v>
       </c>
@@ -4293,7 +4297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="198" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="83" spans="1:5" ht="198" hidden="1" customHeight="1">
       <c r="A83" s="95">
         <v>5</v>
       </c>
@@ -4310,7 +4314,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="84" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A84" s="95">
         <v>5</v>
       </c>
@@ -4327,7 +4331,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="148.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="85" spans="1:5" ht="148.5" hidden="1" customHeight="1">
       <c r="A85" s="95">
         <v>5</v>
       </c>
@@ -4344,7 +4348,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="86" spans="1:5" ht="132" hidden="1" customHeight="1">
       <c r="A86" s="95">
         <v>5</v>
       </c>
@@ -4361,7 +4365,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="87" spans="1:5" ht="99" hidden="1" customHeight="1">
       <c r="A87" s="96">
         <v>5</v>
       </c>
@@ -4378,7 +4382,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="132.30000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:5" ht="132.25" customHeight="1" thickBot="1">
       <c r="A88" s="97">
         <v>5</v>
       </c>
@@ -4395,7 +4399,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="313.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="89" spans="1:5" ht="313.5" customHeight="1">
       <c r="A89" s="98">
         <v>6</v>
       </c>
@@ -4412,7 +4416,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="90" spans="1:5" ht="115.5" hidden="1" customHeight="1">
       <c r="A90" s="99">
         <v>6</v>
       </c>
@@ -4429,7 +4433,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="91" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A91" s="99">
         <v>6</v>
       </c>
@@ -4446,7 +4450,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="92" spans="1:5" ht="99" hidden="1" customHeight="1">
       <c r="A92" s="99">
         <v>6</v>
       </c>
@@ -4463,7 +4467,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="93" spans="1:5" ht="132" hidden="1" customHeight="1">
       <c r="A93" s="99">
         <v>6</v>
       </c>
@@ -4480,7 +4484,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="94" spans="1:5" ht="49.5" hidden="1" customHeight="1">
       <c r="A94" s="99">
         <v>6</v>
       </c>
@@ -4497,7 +4501,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="95" spans="1:5" ht="132" hidden="1" customHeight="1">
       <c r="A95" s="99">
         <v>6</v>
       </c>
@@ -4514,7 +4518,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="96" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A96" s="99">
         <v>6</v>
       </c>
@@ -4531,7 +4535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="97" spans="1:5" ht="132" hidden="1" customHeight="1">
       <c r="A97" s="99">
         <v>6</v>
       </c>
@@ -4548,7 +4552,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="98" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A98" s="99">
         <v>6</v>
       </c>
@@ -4565,7 +4569,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="99" spans="1:5" ht="14.25" hidden="1" customHeight="1">
       <c r="A99" s="99">
         <v>6</v>
       </c>
@@ -4582,7 +4586,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="231.3" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:5" ht="231.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A100" s="100">
         <v>6</v>
       </c>
@@ -4599,7 +4603,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="101" spans="1:5" ht="99" customHeight="1">
       <c r="A101" s="31">
         <v>7</v>
       </c>
@@ -4616,7 +4620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="102" spans="1:5" ht="115.5" customHeight="1">
       <c r="A102" s="31">
         <v>7</v>
       </c>
@@ -4633,7 +4637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="103" spans="1:5" hidden="1">
       <c r="A103" s="31">
         <v>7</v>
       </c>
@@ -4650,7 +4654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="104" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A104" s="31">
         <v>7</v>
       </c>
@@ -4667,7 +4671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="105" spans="1:5" ht="33" customHeight="1">
       <c r="A105" s="31">
         <v>7</v>
       </c>
@@ -4684,7 +4688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="106" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A106" s="31">
         <v>7</v>
       </c>
@@ -4701,7 +4705,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="107" spans="1:5" ht="165" hidden="1" customHeight="1">
       <c r="A107" s="31">
         <v>7</v>
       </c>
@@ -4718,7 +4722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="108" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A108" s="31">
         <v>7</v>
       </c>
@@ -4735,7 +4739,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="148.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="109" spans="1:5" ht="148.5" customHeight="1">
       <c r="A109" s="31">
         <v>7</v>
       </c>
@@ -4752,7 +4756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="110" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A110" s="31">
         <v>7</v>
       </c>
@@ -4769,7 +4773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="111" spans="1:5" ht="66" hidden="1" customHeight="1">
       <c r="A111" s="31">
         <v>7</v>
       </c>
@@ -4786,7 +4790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="112" spans="1:5" hidden="1">
       <c r="A112" s="31">
         <v>7</v>
       </c>
@@ -4803,7 +4807,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="113" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A113" s="31">
         <v>7</v>
       </c>
@@ -4820,7 +4824,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="114" spans="1:5" ht="66" hidden="1" customHeight="1">
       <c r="A114" s="31">
         <v>7</v>
       </c>
@@ -4837,7 +4841,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="115" spans="1:5" hidden="1">
       <c r="A115" s="31">
         <v>7</v>
       </c>
@@ -4854,7 +4858,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="116" spans="1:5" hidden="1">
       <c r="A116" s="31">
         <v>7</v>
       </c>
@@ -4871,7 +4875,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="117" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A117" s="31">
         <v>7</v>
       </c>
@@ -4888,7 +4892,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="118" spans="1:5" ht="115.5" hidden="1" customHeight="1">
       <c r="A118" s="31">
         <v>7</v>
       </c>
@@ -4905,7 +4909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="119" spans="1:5" hidden="1">
       <c r="A119" s="31">
         <v>7</v>
       </c>
@@ -4922,7 +4926,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="120" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A120" s="31">
         <v>7</v>
       </c>
@@ -4939,7 +4943,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="165" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="121" spans="1:5" ht="165" customHeight="1">
       <c r="A121" s="101">
         <v>8</v>
       </c>
@@ -4956,7 +4960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="122" spans="1:5" ht="66" customHeight="1">
       <c r="A122" s="101">
         <v>8</v>
       </c>
@@ -4973,7 +4977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="123" spans="1:5" ht="49.5" hidden="1" customHeight="1">
       <c r="A123" s="101">
         <v>8</v>
       </c>
@@ -4990,7 +4994,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="124" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A124" s="101">
         <v>8</v>
       </c>
@@ -5007,7 +5011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="125" spans="1:5" ht="33" customHeight="1">
       <c r="A125" s="101">
         <v>8</v>
       </c>
@@ -5024,7 +5028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="126" spans="1:5" hidden="1">
       <c r="A126" s="101">
         <v>8</v>
       </c>
@@ -5041,7 +5045,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="127" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A127" s="101">
         <v>8</v>
       </c>
@@ -5058,7 +5062,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="128" spans="1:5" hidden="1">
       <c r="A128" s="101">
         <v>8</v>
       </c>
@@ -5075,7 +5079,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="129" spans="1:5" ht="49.5" customHeight="1">
       <c r="A129" s="101">
         <v>8</v>
       </c>
@@ -5092,7 +5096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="130" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A130" s="101">
         <v>8</v>
       </c>
@@ -5109,7 +5113,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="131" spans="1:5" ht="66" hidden="1" customHeight="1">
       <c r="A131" s="101">
         <v>8</v>
       </c>
@@ -5126,7 +5130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="132" spans="1:5" hidden="1">
       <c r="A132" s="101">
         <v>8</v>
       </c>
@@ -5143,7 +5147,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="133" spans="1:5" ht="99" hidden="1" customHeight="1">
       <c r="A133" s="102">
         <v>9</v>
       </c>
@@ -5160,7 +5164,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="134" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A134" s="102">
         <v>9</v>
       </c>
@@ -5177,7 +5181,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="135" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A135" s="102">
         <v>9</v>
       </c>
@@ -5194,7 +5198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="136" spans="1:5" hidden="1">
       <c r="A136" s="102">
         <v>9</v>
       </c>
@@ -5211,7 +5215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="137" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A137" s="102">
         <v>9</v>
       </c>
@@ -5228,7 +5232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="138" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A138" s="102">
         <v>9</v>
       </c>
@@ -5245,7 +5249,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="139" spans="1:5" ht="49.5" hidden="1" customHeight="1">
       <c r="A139" s="102">
         <v>9</v>
       </c>
@@ -5262,7 +5266,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="140" spans="1:5" ht="49.5" hidden="1" customHeight="1">
       <c r="A140" s="102">
         <v>9</v>
       </c>
@@ -5279,7 +5283,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="141" spans="1:5" ht="49.5" hidden="1" customHeight="1">
       <c r="A141" s="102">
         <v>9</v>
       </c>
@@ -5296,7 +5300,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="142" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A142" s="102">
         <v>9</v>
       </c>
@@ -5313,7 +5317,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="143" spans="1:5" ht="99" hidden="1" customHeight="1">
       <c r="A143" s="102">
         <v>9</v>
       </c>
@@ -5330,7 +5334,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="144" spans="1:5" hidden="1">
       <c r="A144" s="102">
         <v>9</v>
       </c>
@@ -5347,7 +5351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="115.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="145" spans="1:5" ht="115.5" hidden="1" customHeight="1">
       <c r="A145" s="103">
         <v>10</v>
       </c>
@@ -5364,7 +5368,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="146" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A146" s="103">
         <v>10</v>
       </c>
@@ -5381,7 +5385,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="147" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A147" s="103">
         <v>10</v>
       </c>
@@ -5398,7 +5402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="148" spans="1:5" hidden="1">
       <c r="A148" s="103">
         <v>10</v>
       </c>
@@ -5415,7 +5419,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="149" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A149" s="103">
         <v>10</v>
       </c>
@@ -5432,7 +5436,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="150" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A150" s="103">
         <v>10</v>
       </c>
@@ -5449,7 +5453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="151" spans="1:5" hidden="1">
       <c r="A151" s="103">
         <v>10</v>
       </c>
@@ -5466,7 +5470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="152" spans="1:5" hidden="1">
       <c r="A152" s="103">
         <v>10</v>
       </c>
@@ -5483,7 +5487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="153" spans="1:5" hidden="1">
       <c r="A153" s="103">
         <v>10</v>
       </c>
@@ -5500,7 +5504,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="154" spans="1:5" hidden="1">
       <c r="A154" s="103">
         <v>10</v>
       </c>
@@ -5517,7 +5521,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="155" spans="1:5" hidden="1">
       <c r="A155" s="103">
         <v>10</v>
       </c>
@@ -5534,7 +5538,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="156" spans="1:5" ht="99" hidden="1" customHeight="1">
       <c r="A156" s="103">
         <v>10</v>
       </c>
@@ -5551,7 +5555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="157" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A157" s="103">
         <v>10</v>
       </c>
@@ -5568,7 +5572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="158" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A158" s="103">
         <v>10</v>
       </c>
@@ -5585,7 +5589,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="159" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A159" s="109">
         <v>11</v>
       </c>
@@ -5602,7 +5606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="160" spans="1:5" ht="132" hidden="1" customHeight="1">
       <c r="A160" s="109">
         <v>11</v>
       </c>
@@ -5619,7 +5623,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="161" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A161" s="97">
         <v>11</v>
       </c>
@@ -5636,7 +5640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="162" spans="1:5" ht="49.5" hidden="1" customHeight="1">
       <c r="A162" s="109">
         <v>11</v>
       </c>
@@ -5653,7 +5657,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="66" x14ac:dyDescent="0.7">
+    <row r="163" spans="1:5" ht="68" hidden="1">
       <c r="A163" s="109">
         <v>11</v>
       </c>
@@ -5670,7 +5674,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="164" spans="1:5" ht="49.5" hidden="1" customHeight="1">
       <c r="A164" s="109">
         <v>11</v>
       </c>
@@ -5687,7 +5691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="165" spans="1:5" hidden="1">
       <c r="A165" s="109">
         <v>11</v>
       </c>
@@ -5704,7 +5708,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="166" spans="1:5" ht="66" hidden="1" customHeight="1">
       <c r="A166" s="109">
         <v>11</v>
       </c>
@@ -5721,7 +5725,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="167" spans="1:5" hidden="1">
       <c r="A167" s="109">
         <v>11</v>
       </c>
@@ -5738,7 +5742,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="168" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A168" s="109">
         <v>11</v>
       </c>
@@ -5755,7 +5759,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="169" spans="1:5" hidden="1">
       <c r="A169" s="109">
         <v>11</v>
       </c>
@@ -5772,7 +5776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="170" spans="1:5" ht="82.5" hidden="1" customHeight="1">
       <c r="A170" s="109">
         <v>11</v>
       </c>
@@ -5789,7 +5793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="171" spans="1:5" hidden="1">
       <c r="A171" s="109">
         <v>11</v>
       </c>
@@ -5806,7 +5810,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="172" spans="1:5" hidden="1">
       <c r="A172" s="109">
         <v>11</v>
       </c>
@@ -5823,7 +5827,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="173" spans="1:5" hidden="1">
       <c r="A173" s="109">
         <v>11</v>
       </c>
@@ -5840,7 +5844,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="174" spans="1:5" hidden="1">
       <c r="A174" s="109">
         <v>11</v>
       </c>
@@ -5857,7 +5861,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="175" spans="1:5" ht="66" hidden="1" customHeight="1">
       <c r="A175" s="109">
         <v>11</v>
       </c>
@@ -5874,7 +5878,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="176" spans="1:5" hidden="1">
       <c r="A176" s="109">
         <v>11</v>
       </c>
@@ -5891,7 +5895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="177" spans="1:5" hidden="1">
       <c r="A177" s="109">
         <v>11</v>
       </c>
@@ -5908,7 +5912,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="178" spans="1:5" hidden="1">
       <c r="A178" s="109">
         <v>11</v>
       </c>
@@ -5925,7 +5929,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="179" spans="1:5" ht="49.5" hidden="1" customHeight="1">
       <c r="A179" s="109">
         <v>11</v>
       </c>
@@ -5942,7 +5946,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="180" spans="1:5" hidden="1">
       <c r="A180" s="109">
         <v>11</v>
       </c>
@@ -5957,7 +5961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="181" spans="1:5" hidden="1">
       <c r="A181" s="110">
         <v>12</v>
       </c>
@@ -5972,7 +5976,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="182" spans="1:5" hidden="1">
       <c r="A182" s="110">
         <v>12</v>
       </c>
@@ -5987,7 +5991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="183" spans="1:5" hidden="1">
       <c r="A183" s="110">
         <v>12</v>
       </c>
@@ -6002,7 +6006,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="184" spans="1:5" hidden="1">
       <c r="A184" s="110">
         <v>12</v>
       </c>
@@ -6017,7 +6021,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="185" spans="1:5" hidden="1">
       <c r="A185" s="110">
         <v>12</v>
       </c>
@@ -6032,7 +6036,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="186" spans="1:5" hidden="1">
       <c r="A186" s="110">
         <v>12</v>
       </c>
@@ -6047,7 +6051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="187" spans="1:5" hidden="1">
       <c r="A187" s="110">
         <v>12</v>
       </c>
@@ -6062,7 +6066,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="188" spans="1:5" hidden="1">
       <c r="A188" s="110">
         <v>12</v>
       </c>
@@ -6077,7 +6081,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="189" spans="1:5" hidden="1">
       <c r="A189" s="110">
         <v>12</v>
       </c>
@@ -6092,7 +6096,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="190" spans="1:5" hidden="1">
       <c r="A190" s="110">
         <v>12</v>
       </c>
@@ -6107,7 +6111,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="191" spans="1:5" hidden="1">
       <c r="A191" s="110">
         <v>12</v>
       </c>
@@ -6122,7 +6126,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="192" spans="1:5" hidden="1">
       <c r="A192" s="110">
         <v>12</v>
       </c>
@@ -6137,7 +6141,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="193" spans="1:5" hidden="1">
       <c r="A193" s="110">
         <v>12</v>
       </c>
@@ -6152,7 +6156,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="194" spans="1:5" hidden="1">
       <c r="A194" s="110">
         <v>12</v>
       </c>
@@ -6167,7 +6171,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="195" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A195" s="110">
         <v>12</v>
       </c>
@@ -6184,7 +6188,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="196" spans="1:5" hidden="1">
       <c r="A196" s="110">
         <v>12</v>
       </c>
@@ -6201,7 +6205,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="197" spans="1:5" hidden="1">
       <c r="A197" s="110">
         <v>12</v>
       </c>
@@ -6218,2864 +6222,2871 @@
         <v>19</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="198" spans="1:5">
       <c r="A198" s="111"/>
       <c r="B198" s="112"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="199" spans="1:5">
       <c r="A199" s="111"/>
       <c r="B199" s="112"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="200" spans="1:5">
       <c r="A200" s="111"/>
       <c r="B200" s="112"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="201" spans="1:5">
       <c r="A201" s="111"/>
       <c r="B201" s="112"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="202" spans="1:5">
       <c r="A202" s="111"/>
       <c r="B202" s="112"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="203" spans="1:5">
       <c r="A203" s="111"/>
       <c r="B203" s="112"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="204" spans="1:5">
       <c r="A204" s="111"/>
       <c r="B204" s="112"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="205" spans="1:5">
       <c r="A205" s="111"/>
       <c r="B205" s="112"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="206" spans="1:5">
       <c r="A206" s="111"/>
       <c r="B206" s="112"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="207" spans="1:5">
       <c r="A207" s="111"/>
       <c r="B207" s="112"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.7">
+    <row r="208" spans="1:5">
       <c r="A208" s="111"/>
       <c r="B208" s="112"/>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="209" spans="1:2">
       <c r="A209" s="111"/>
       <c r="B209" s="112"/>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="210" spans="1:2">
       <c r="A210" s="111"/>
       <c r="B210" s="112"/>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="211" spans="1:2">
       <c r="A211" s="111"/>
       <c r="B211" s="112"/>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="212" spans="1:2">
       <c r="A212" s="111"/>
       <c r="B212" s="112"/>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="213" spans="1:2">
       <c r="A213" s="111"/>
       <c r="B213" s="112"/>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="214" spans="1:2">
       <c r="A214" s="111"/>
       <c r="B214" s="112"/>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="215" spans="1:2">
       <c r="A215" s="111"/>
       <c r="B215" s="112"/>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="216" spans="1:2">
       <c r="A216" s="111"/>
       <c r="B216" s="112"/>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="217" spans="1:2">
       <c r="A217" s="111"/>
       <c r="B217" s="112"/>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="218" spans="1:2">
       <c r="A218" s="111"/>
       <c r="B218" s="112"/>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="219" spans="1:2">
       <c r="A219" s="111"/>
       <c r="B219" s="112"/>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="220" spans="1:2">
       <c r="A220" s="111"/>
       <c r="B220" s="112"/>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="221" spans="1:2">
       <c r="A221" s="111"/>
       <c r="B221" s="112"/>
     </row>
-    <row r="222" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="222" spans="1:2" ht="16.5" customHeight="1">
       <c r="A222" s="111"/>
       <c r="B222" s="112"/>
     </row>
-    <row r="223" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="223" spans="1:2" ht="16.5" customHeight="1">
       <c r="A223" s="111"/>
       <c r="B223" s="112"/>
     </row>
-    <row r="224" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="224" spans="1:2" ht="16.5" customHeight="1">
       <c r="A224" s="111"/>
       <c r="B224" s="112"/>
     </row>
-    <row r="225" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="225" spans="1:2" ht="16.5" customHeight="1">
       <c r="A225" s="111"/>
       <c r="B225" s="112"/>
     </row>
-    <row r="226" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="226" spans="1:2" ht="16.5" customHeight="1">
       <c r="A226" s="111"/>
       <c r="B226" s="112"/>
     </row>
-    <row r="227" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="227" spans="1:2" ht="16.5" customHeight="1">
       <c r="A227" s="111"/>
       <c r="B227" s="112"/>
     </row>
-    <row r="228" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="228" spans="1:2" ht="16.5" customHeight="1">
       <c r="A228" s="111"/>
       <c r="B228" s="112"/>
     </row>
-    <row r="229" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="229" spans="1:2" ht="16.5" customHeight="1">
       <c r="A229" s="111"/>
       <c r="B229" s="112"/>
     </row>
-    <row r="230" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="230" spans="1:2" ht="16.5" customHeight="1">
       <c r="A230" s="111"/>
       <c r="B230" s="112"/>
     </row>
-    <row r="231" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="231" spans="1:2" ht="16.5" customHeight="1">
       <c r="A231" s="111"/>
       <c r="B231" s="112"/>
     </row>
-    <row r="232" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="232" spans="1:2" ht="16.5" customHeight="1">
       <c r="A232" s="111"/>
       <c r="B232" s="112"/>
     </row>
-    <row r="233" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="233" spans="1:2" ht="16.5" customHeight="1">
       <c r="A233" s="111"/>
       <c r="B233" s="112"/>
     </row>
-    <row r="234" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="234" spans="1:2" ht="16.5" customHeight="1">
       <c r="A234" s="111"/>
       <c r="B234" s="112"/>
     </row>
-    <row r="235" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="235" spans="1:2" ht="16.5" customHeight="1">
       <c r="A235" s="111"/>
       <c r="B235" s="112"/>
     </row>
-    <row r="236" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="236" spans="1:2" ht="16.5" customHeight="1">
       <c r="A236" s="111"/>
       <c r="B236" s="112"/>
     </row>
-    <row r="237" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="237" spans="1:2" ht="16.5" customHeight="1">
       <c r="A237" s="111"/>
       <c r="B237" s="112"/>
     </row>
-    <row r="238" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="238" spans="1:2" ht="16.5" customHeight="1">
       <c r="A238" s="111"/>
       <c r="B238" s="112"/>
     </row>
-    <row r="239" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="239" spans="1:2" ht="16.5" customHeight="1">
       <c r="A239" s="111"/>
       <c r="B239" s="112"/>
     </row>
-    <row r="240" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="240" spans="1:2" ht="16.5" customHeight="1">
       <c r="A240" s="111"/>
       <c r="B240" s="112"/>
     </row>
-    <row r="241" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="241" spans="1:2" ht="16.5" customHeight="1">
       <c r="A241" s="111"/>
       <c r="B241" s="112"/>
     </row>
-    <row r="242" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="242" spans="1:2" ht="16.5" customHeight="1">
       <c r="A242" s="111"/>
       <c r="B242" s="112"/>
     </row>
-    <row r="243" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="243" spans="1:2" ht="16.5" customHeight="1">
       <c r="A243" s="111"/>
       <c r="B243" s="112"/>
     </row>
-    <row r="244" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="244" spans="1:2" ht="16.5" customHeight="1">
       <c r="A244" s="111"/>
       <c r="B244" s="112"/>
     </row>
-    <row r="245" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="245" spans="1:2" ht="16.5" customHeight="1">
       <c r="A245" s="111"/>
       <c r="B245" s="112"/>
     </row>
-    <row r="246" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="246" spans="1:2" ht="16.5" customHeight="1">
       <c r="A246" s="111"/>
       <c r="B246" s="112"/>
     </row>
-    <row r="247" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="247" spans="1:2" ht="16.5" customHeight="1">
       <c r="A247" s="111"/>
       <c r="B247" s="112"/>
     </row>
-    <row r="248" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="248" spans="1:2" ht="16.5" customHeight="1">
       <c r="A248" s="111"/>
       <c r="B248" s="112"/>
     </row>
-    <row r="249" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="249" spans="1:2" ht="16.5" customHeight="1">
       <c r="A249" s="111"/>
       <c r="B249" s="112"/>
     </row>
-    <row r="250" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="250" spans="1:2" ht="16.5" customHeight="1">
       <c r="A250" s="111"/>
       <c r="B250" s="112"/>
     </row>
-    <row r="251" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="251" spans="1:2" ht="16.5" customHeight="1">
       <c r="A251" s="111"/>
       <c r="B251" s="112"/>
     </row>
-    <row r="252" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="252" spans="1:2" ht="16.5" customHeight="1">
       <c r="A252" s="111"/>
       <c r="B252" s="112"/>
     </row>
-    <row r="253" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="253" spans="1:2" ht="16.5" customHeight="1">
       <c r="A253" s="111"/>
       <c r="B253" s="112"/>
     </row>
-    <row r="254" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="254" spans="1:2" ht="16.5" customHeight="1">
       <c r="A254" s="111"/>
       <c r="B254" s="112"/>
     </row>
-    <row r="255" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="255" spans="1:2" ht="16.5" customHeight="1">
       <c r="A255" s="111"/>
       <c r="B255" s="112"/>
     </row>
-    <row r="256" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="256" spans="1:2" ht="16.5" customHeight="1">
       <c r="A256" s="111"/>
       <c r="B256" s="112"/>
     </row>
-    <row r="257" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="257" spans="1:2" ht="16.5" customHeight="1">
       <c r="A257" s="111"/>
       <c r="B257" s="112"/>
     </row>
-    <row r="258" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="258" spans="1:2" ht="16.5" customHeight="1">
       <c r="A258" s="111"/>
       <c r="B258" s="112"/>
     </row>
-    <row r="259" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="259" spans="1:2" ht="16.5" customHeight="1">
       <c r="A259" s="111"/>
       <c r="B259" s="112"/>
     </row>
-    <row r="260" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="260" spans="1:2" ht="16.5" customHeight="1">
       <c r="A260" s="111"/>
       <c r="B260" s="112"/>
     </row>
-    <row r="261" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="261" spans="1:2" ht="16.5" customHeight="1">
       <c r="A261" s="111"/>
       <c r="B261" s="112"/>
     </row>
-    <row r="262" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="262" spans="1:2" ht="16.5" customHeight="1">
       <c r="A262" s="111"/>
       <c r="B262" s="112"/>
     </row>
-    <row r="263" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="263" spans="1:2" ht="16.5" customHeight="1">
       <c r="A263" s="111"/>
       <c r="B263" s="112"/>
     </row>
-    <row r="264" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="264" spans="1:2" ht="16.5" customHeight="1">
       <c r="A264" s="111"/>
       <c r="B264" s="112"/>
     </row>
-    <row r="265" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="265" spans="1:2" ht="16.5" customHeight="1">
       <c r="A265" s="111"/>
       <c r="B265" s="112"/>
     </row>
-    <row r="266" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="266" spans="1:2" ht="33" customHeight="1">
       <c r="A266" s="111"/>
       <c r="B266" s="112"/>
     </row>
-    <row r="267" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="267" spans="1:2" ht="16.5" customHeight="1">
       <c r="A267" s="111"/>
       <c r="B267" s="112"/>
     </row>
-    <row r="268" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="268" spans="1:2" ht="16.5" customHeight="1">
       <c r="A268" s="111"/>
       <c r="B268" s="112"/>
     </row>
-    <row r="269" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="269" spans="1:2" ht="16.5" customHeight="1">
       <c r="A269" s="111"/>
       <c r="B269" s="112"/>
     </row>
-    <row r="270" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="270" spans="1:2" ht="16.5" customHeight="1">
       <c r="A270" s="111"/>
       <c r="B270" s="112"/>
     </row>
-    <row r="271" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="271" spans="1:2" ht="16.5" customHeight="1">
       <c r="A271" s="111"/>
       <c r="B271" s="112"/>
     </row>
-    <row r="272" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="272" spans="1:2" ht="16.5" customHeight="1">
       <c r="A272" s="111"/>
       <c r="B272" s="112"/>
     </row>
-    <row r="273" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="273" spans="1:2" ht="33" customHeight="1">
       <c r="A273" s="111"/>
       <c r="B273" s="112"/>
     </row>
-    <row r="274" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="274" spans="1:2" ht="16.5" customHeight="1">
       <c r="A274" s="111"/>
       <c r="B274" s="112"/>
     </row>
-    <row r="275" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="275" spans="1:2" ht="16.5" customHeight="1">
       <c r="A275" s="111"/>
       <c r="B275" s="112"/>
     </row>
-    <row r="276" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="276" spans="1:2" ht="16.5" customHeight="1">
       <c r="A276" s="111"/>
       <c r="B276" s="112"/>
     </row>
-    <row r="277" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="277" spans="1:2" ht="16.5" customHeight="1">
       <c r="A277" s="111"/>
       <c r="B277" s="112"/>
     </row>
-    <row r="278" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="278" spans="1:2" ht="16.5" customHeight="1">
       <c r="A278" s="111"/>
       <c r="B278" s="112"/>
     </row>
-    <row r="279" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="279" spans="1:2" ht="16.5" customHeight="1">
       <c r="A279" s="111"/>
       <c r="B279" s="112"/>
     </row>
-    <row r="280" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="280" spans="1:2" ht="16.5" customHeight="1">
       <c r="A280" s="111"/>
       <c r="B280" s="112"/>
     </row>
-    <row r="281" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="281" spans="1:2" ht="16.5" customHeight="1">
       <c r="A281" s="111"/>
       <c r="B281" s="112"/>
     </row>
-    <row r="282" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="282" spans="1:2" ht="16.5" customHeight="1">
       <c r="A282" s="111"/>
       <c r="B282" s="112"/>
     </row>
-    <row r="283" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="283" spans="1:2" ht="16.5" customHeight="1">
       <c r="A283" s="111"/>
       <c r="B283" s="112"/>
     </row>
-    <row r="284" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="284" spans="1:2" ht="16.5" customHeight="1">
       <c r="A284" s="111"/>
       <c r="B284" s="112"/>
     </row>
-    <row r="285" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="285" spans="1:2" ht="16.5" customHeight="1">
       <c r="A285" s="111"/>
       <c r="B285" s="112"/>
     </row>
-    <row r="286" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="286" spans="1:2" ht="17.25" customHeight="1">
       <c r="A286" s="111"/>
       <c r="B286" s="112"/>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="287" spans="1:2">
       <c r="A287" s="111"/>
       <c r="B287" s="112"/>
     </row>
-    <row r="288" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="288" spans="1:2" ht="17.25" customHeight="1">
       <c r="A288" s="111"/>
       <c r="B288" s="112"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="289" spans="1:2">
       <c r="A289" s="111"/>
       <c r="B289" s="112"/>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="290" spans="1:2">
       <c r="A290" s="111"/>
       <c r="B290" s="112"/>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="291" spans="1:2">
       <c r="A291" s="111"/>
       <c r="B291" s="112"/>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="292" spans="1:2">
       <c r="A292" s="111"/>
       <c r="B292" s="112"/>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="293" spans="1:2">
       <c r="A293" s="111"/>
       <c r="B293" s="112"/>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="294" spans="1:2">
       <c r="A294" s="111"/>
       <c r="B294" s="112"/>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="295" spans="1:2">
       <c r="A295" s="111"/>
       <c r="B295" s="112"/>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="296" spans="1:2">
       <c r="A296" s="111"/>
       <c r="B296" s="112"/>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="297" spans="1:2">
       <c r="A297" s="111"/>
       <c r="B297" s="112"/>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="298" spans="1:2">
       <c r="A298" s="111"/>
       <c r="B298" s="112"/>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="299" spans="1:2">
       <c r="A299" s="111"/>
       <c r="B299" s="112"/>
     </row>
-    <row r="300" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="300" spans="1:2" ht="16.5" customHeight="1">
       <c r="A300" s="111"/>
       <c r="B300" s="112"/>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="301" spans="1:2">
       <c r="A301" s="111"/>
       <c r="B301" s="112"/>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="302" spans="1:2">
       <c r="A302" s="111"/>
       <c r="B302" s="112"/>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="303" spans="1:2">
       <c r="A303" s="111"/>
       <c r="B303" s="112"/>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="304" spans="1:2">
       <c r="A304" s="111"/>
       <c r="B304" s="112"/>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="305" spans="1:2">
       <c r="A305" s="111"/>
       <c r="B305" s="112"/>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="306" spans="1:2">
       <c r="A306" s="111"/>
       <c r="B306" s="112"/>
     </row>
-    <row r="307" spans="1:2" ht="70" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="307" spans="1:2" ht="70" customHeight="1">
       <c r="A307" s="111"/>
       <c r="B307" s="112"/>
     </row>
-    <row r="308" spans="1:2" ht="70" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="308" spans="1:2" ht="70" customHeight="1">
       <c r="A308" s="111"/>
       <c r="B308" s="112"/>
     </row>
-    <row r="309" spans="1:2" ht="70" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="309" spans="1:2" ht="70" customHeight="1">
       <c r="A309" s="111"/>
       <c r="B309" s="112"/>
     </row>
-    <row r="310" spans="1:2" ht="70" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="310" spans="1:2" ht="70" customHeight="1">
       <c r="A310" s="111"/>
       <c r="B310" s="112"/>
     </row>
-    <row r="311" spans="1:2" ht="70" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="311" spans="1:2" ht="70" customHeight="1">
       <c r="A311" s="111"/>
       <c r="B311" s="112"/>
     </row>
-    <row r="312" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="312" spans="1:2" ht="16.5" customHeight="1">
       <c r="A312" s="111"/>
       <c r="B312" s="112"/>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="313" spans="1:2">
       <c r="A313" s="111"/>
       <c r="B313" s="112"/>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="314" spans="1:2">
       <c r="A314" s="111"/>
       <c r="B314" s="112"/>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="315" spans="1:2">
       <c r="A315" s="111"/>
       <c r="B315" s="112"/>
     </row>
-    <row r="316" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="316" spans="1:2" ht="16.5" customHeight="1">
       <c r="A316" s="111"/>
       <c r="B316" s="112"/>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="317" spans="1:2">
       <c r="A317" s="111"/>
       <c r="B317" s="112"/>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="318" spans="1:2">
       <c r="A318" s="111"/>
       <c r="B318" s="112"/>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="319" spans="1:2">
       <c r="A319" s="111"/>
       <c r="B319" s="112"/>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="320" spans="1:2">
       <c r="A320" s="111"/>
       <c r="B320" s="112"/>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="321" spans="1:2">
       <c r="A321" s="111"/>
       <c r="B321" s="112"/>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="322" spans="1:2">
       <c r="A322" s="111"/>
       <c r="B322" s="112"/>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="323" spans="1:2">
       <c r="A323" s="111"/>
       <c r="B323" s="112"/>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="324" spans="1:2">
       <c r="A324" s="111"/>
       <c r="B324" s="112"/>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="325" spans="1:2">
       <c r="A325" s="111"/>
       <c r="B325" s="112"/>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="326" spans="1:2">
       <c r="A326" s="111"/>
       <c r="B326" s="112"/>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="327" spans="1:2">
       <c r="A327" s="111"/>
       <c r="B327" s="112"/>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="328" spans="1:2">
       <c r="A328" s="111"/>
       <c r="B328" s="112"/>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="329" spans="1:2">
       <c r="A329" s="111"/>
       <c r="B329" s="112"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="330" spans="1:2">
       <c r="A330" s="111"/>
       <c r="B330" s="112"/>
     </row>
-    <row r="331" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="331" spans="1:2" ht="16.5" customHeight="1">
       <c r="A331" s="111"/>
       <c r="B331" s="112"/>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="332" spans="1:2">
       <c r="A332" s="111"/>
       <c r="B332" s="112"/>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="333" spans="1:2">
       <c r="A333" s="111"/>
       <c r="B333" s="112"/>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="334" spans="1:2">
       <c r="A334" s="111"/>
       <c r="B334" s="112"/>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="335" spans="1:2">
       <c r="A335" s="111"/>
       <c r="B335" s="112"/>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="336" spans="1:2">
       <c r="A336" s="111"/>
       <c r="B336" s="112"/>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="337" spans="1:2">
       <c r="A337" s="111"/>
       <c r="B337" s="112"/>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="338" spans="1:2">
       <c r="A338" s="111"/>
       <c r="B338" s="112"/>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="339" spans="1:2">
       <c r="A339" s="111"/>
       <c r="B339" s="112"/>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="340" spans="1:2">
       <c r="A340" s="111"/>
       <c r="B340" s="112"/>
     </row>
-    <row r="341" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="341" spans="1:2" ht="16.5" customHeight="1">
       <c r="A341" s="111"/>
       <c r="B341" s="112"/>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="342" spans="1:2">
       <c r="A342" s="111"/>
       <c r="B342" s="112"/>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="343" spans="1:2">
       <c r="A343" s="111"/>
       <c r="B343" s="112"/>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="344" spans="1:2">
       <c r="A344" s="111"/>
       <c r="B344" s="112"/>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="345" spans="1:2">
       <c r="A345" s="111"/>
       <c r="B345" s="112"/>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="346" spans="1:2">
       <c r="A346" s="111"/>
       <c r="B346" s="112"/>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="347" spans="1:2">
       <c r="A347" s="111"/>
       <c r="B347" s="112"/>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="348" spans="1:2">
       <c r="A348" s="111"/>
       <c r="B348" s="112"/>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="349" spans="1:2">
       <c r="A349" s="111"/>
       <c r="B349" s="112"/>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="350" spans="1:2">
       <c r="A350" s="111"/>
       <c r="B350" s="112"/>
     </row>
-    <row r="351" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="351" spans="1:2" ht="16.5" customHeight="1">
       <c r="A351" s="111"/>
       <c r="B351" s="112"/>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="352" spans="1:2">
       <c r="A352" s="111"/>
       <c r="B352" s="112"/>
     </row>
-    <row r="353" spans="1:2" ht="99" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="353" spans="1:2" ht="99" customHeight="1">
       <c r="A353" s="111"/>
       <c r="B353" s="112"/>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="354" spans="1:2">
       <c r="A354" s="111"/>
       <c r="B354" s="112"/>
     </row>
-    <row r="355" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="355" spans="1:2" ht="16.5" customHeight="1">
       <c r="A355" s="111"/>
       <c r="B355" s="112"/>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="356" spans="1:2">
       <c r="A356" s="111"/>
       <c r="B356" s="112"/>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="357" spans="1:2">
       <c r="A357" s="111"/>
       <c r="B357" s="112"/>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="358" spans="1:2">
       <c r="A358" s="111"/>
       <c r="B358" s="112"/>
     </row>
-    <row r="359" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="359" spans="1:2" ht="16.5" customHeight="1">
       <c r="A359" s="111"/>
       <c r="B359" s="112"/>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="360" spans="1:2">
       <c r="A360" s="111"/>
       <c r="B360" s="112"/>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="361" spans="1:2">
       <c r="A361" s="111"/>
       <c r="B361" s="112"/>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="362" spans="1:2">
       <c r="A362" s="111"/>
       <c r="B362" s="112"/>
     </row>
-    <row r="363" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="363" spans="1:2" ht="16.5" customHeight="1">
       <c r="A363" s="111"/>
       <c r="B363" s="112"/>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="364" spans="1:2">
       <c r="A364" s="111"/>
       <c r="B364" s="112"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="365" spans="1:2">
       <c r="A365" s="111"/>
       <c r="B365" s="112"/>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="366" spans="1:2">
       <c r="A366" s="111"/>
       <c r="B366" s="112"/>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="367" spans="1:2">
       <c r="A367" s="111"/>
       <c r="B367" s="112"/>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="368" spans="1:2">
       <c r="A368" s="111"/>
       <c r="B368" s="112"/>
     </row>
-    <row r="369" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="369" spans="1:2" ht="16.5" customHeight="1">
       <c r="A369" s="111"/>
       <c r="B369" s="112"/>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="370" spans="1:2">
       <c r="A370" s="111"/>
       <c r="B370" s="112"/>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="371" spans="1:2">
       <c r="A371" s="111"/>
       <c r="B371" s="112"/>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="372" spans="1:2">
       <c r="A372" s="111"/>
       <c r="B372" s="112"/>
     </row>
-    <row r="373" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="373" spans="1:2" ht="16.5" customHeight="1">
       <c r="A373" s="111"/>
       <c r="B373" s="112"/>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="374" spans="1:2">
       <c r="A374" s="111"/>
       <c r="B374" s="112"/>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="375" spans="1:2">
       <c r="A375" s="111"/>
       <c r="B375" s="112"/>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="376" spans="1:2">
       <c r="A376" s="111"/>
       <c r="B376" s="112"/>
     </row>
-    <row r="377" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="377" spans="1:2" ht="16.5" customHeight="1">
       <c r="A377" s="111"/>
       <c r="B377" s="112"/>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="378" spans="1:2">
       <c r="A378" s="111"/>
       <c r="B378" s="112"/>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="379" spans="1:2">
       <c r="A379" s="111"/>
       <c r="B379" s="112"/>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="380" spans="1:2">
       <c r="A380" s="111"/>
       <c r="B380" s="112"/>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="381" spans="1:2">
       <c r="A381" s="111"/>
       <c r="B381" s="112"/>
     </row>
-    <row r="382" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="382" spans="1:2" ht="16.5" customHeight="1">
       <c r="A382" s="111"/>
       <c r="B382" s="112"/>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="383" spans="1:2">
       <c r="A383" s="111"/>
       <c r="B383" s="112"/>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="384" spans="1:2">
       <c r="A384" s="111"/>
       <c r="B384" s="112"/>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="385" spans="1:2">
       <c r="A385" s="111"/>
       <c r="B385" s="112"/>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="386" spans="1:2">
       <c r="A386" s="111"/>
       <c r="B386" s="112"/>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="387" spans="1:2">
       <c r="A387" s="111"/>
       <c r="B387" s="112"/>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="388" spans="1:2">
       <c r="A388" s="111"/>
       <c r="B388" s="112"/>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="389" spans="1:2">
       <c r="A389" s="111"/>
       <c r="B389" s="112"/>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="390" spans="1:2">
       <c r="A390" s="111"/>
       <c r="B390" s="112"/>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="391" spans="1:2">
       <c r="A391" s="111"/>
       <c r="B391" s="112"/>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="392" spans="1:2">
       <c r="A392" s="111"/>
       <c r="B392" s="112"/>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="393" spans="1:2">
       <c r="A393" s="111"/>
       <c r="B393" s="112"/>
     </row>
-    <row r="394" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="394" spans="1:2" ht="16.5" customHeight="1">
       <c r="A394" s="111"/>
       <c r="B394" s="112"/>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="395" spans="1:2">
       <c r="A395" s="111"/>
       <c r="B395" s="112"/>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="396" spans="1:2">
       <c r="A396" s="111"/>
       <c r="B396" s="112"/>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="397" spans="1:2">
       <c r="A397" s="111"/>
       <c r="B397" s="112"/>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="398" spans="1:2">
       <c r="A398" s="111"/>
       <c r="B398" s="112"/>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="399" spans="1:2">
       <c r="A399" s="111"/>
       <c r="B399" s="112"/>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="400" spans="1:2">
       <c r="A400" s="111"/>
       <c r="B400" s="112"/>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="401" spans="1:2">
       <c r="A401" s="111"/>
       <c r="B401" s="112"/>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="402" spans="1:2">
       <c r="A402" s="111"/>
       <c r="B402" s="112"/>
     </row>
-    <row r="403" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="403" spans="1:2" ht="17.25" customHeight="1">
       <c r="A403" s="111"/>
       <c r="B403" s="112"/>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="404" spans="1:2">
       <c r="A404" s="111"/>
       <c r="B404" s="112"/>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="405" spans="1:2">
       <c r="A405" s="111"/>
       <c r="B405" s="112"/>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="406" spans="1:2">
       <c r="A406" s="111"/>
       <c r="B406" s="112"/>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="407" spans="1:2">
       <c r="A407" s="111"/>
       <c r="B407" s="112"/>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="408" spans="1:2">
       <c r="A408" s="111"/>
       <c r="B408" s="112"/>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="409" spans="1:2">
       <c r="A409" s="111"/>
       <c r="B409" s="112"/>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="410" spans="1:2">
       <c r="A410" s="111"/>
       <c r="B410" s="112"/>
     </row>
-    <row r="411" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="411" spans="1:2" ht="16.5" customHeight="1">
       <c r="A411" s="111"/>
       <c r="B411" s="112"/>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="412" spans="1:2">
       <c r="A412" s="111"/>
       <c r="B412" s="112"/>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="413" spans="1:2">
       <c r="A413" s="111"/>
       <c r="B413" s="112"/>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="414" spans="1:2">
       <c r="A414" s="111"/>
       <c r="B414" s="112"/>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="415" spans="1:2">
       <c r="A415" s="111"/>
       <c r="B415" s="112"/>
     </row>
-    <row r="416" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="416" spans="1:2" ht="16.5" customHeight="1">
       <c r="A416" s="111"/>
       <c r="B416" s="112"/>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="417" spans="1:2">
       <c r="A417" s="111"/>
       <c r="B417" s="112"/>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="418" spans="1:2">
       <c r="A418" s="111"/>
       <c r="B418" s="112"/>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="419" spans="1:2">
       <c r="A419" s="111"/>
       <c r="B419" s="112"/>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="420" spans="1:2">
       <c r="A420" s="111"/>
       <c r="B420" s="112"/>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="421" spans="1:2">
       <c r="A421" s="111"/>
       <c r="B421" s="112"/>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="422" spans="1:2">
       <c r="A422" s="111"/>
       <c r="B422" s="112"/>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="423" spans="1:2">
       <c r="A423" s="111"/>
       <c r="B423" s="112"/>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="424" spans="1:2">
       <c r="A424" s="111"/>
       <c r="B424" s="112"/>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="425" spans="1:2">
       <c r="A425" s="111"/>
       <c r="B425" s="112"/>
     </row>
-    <row r="426" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="426" spans="1:2" ht="16.5" customHeight="1">
       <c r="A426" s="111"/>
       <c r="B426" s="112"/>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="427" spans="1:2">
       <c r="A427" s="111"/>
       <c r="B427" s="112"/>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="428" spans="1:2">
       <c r="A428" s="111"/>
       <c r="B428" s="112"/>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="429" spans="1:2">
       <c r="A429" s="111"/>
       <c r="B429" s="112"/>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="430" spans="1:2">
       <c r="A430" s="111"/>
       <c r="B430" s="112"/>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="431" spans="1:2">
       <c r="A431" s="111"/>
       <c r="B431" s="112"/>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="432" spans="1:2">
       <c r="A432" s="111"/>
       <c r="B432" s="112"/>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="433" spans="1:2">
       <c r="A433" s="111"/>
       <c r="B433" s="112"/>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="434" spans="1:2">
       <c r="A434" s="111"/>
       <c r="B434" s="112"/>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="435" spans="1:2">
       <c r="A435" s="111"/>
       <c r="B435" s="112"/>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="436" spans="1:2">
       <c r="A436" s="111"/>
       <c r="B436" s="112"/>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="437" spans="1:2">
       <c r="A437" s="111"/>
       <c r="B437" s="112"/>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="438" spans="1:2">
       <c r="A438" s="111"/>
       <c r="B438" s="112"/>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="439" spans="1:2">
       <c r="A439" s="111"/>
       <c r="B439" s="112"/>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="440" spans="1:2">
       <c r="A440" s="111"/>
       <c r="B440" s="112"/>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="441" spans="1:2">
       <c r="A441" s="111"/>
       <c r="B441" s="112"/>
     </row>
-    <row r="442" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="442" spans="1:2" ht="16.5" customHeight="1">
       <c r="A442" s="111"/>
       <c r="B442" s="112"/>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="443" spans="1:2">
       <c r="A443" s="111"/>
       <c r="B443" s="112"/>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="444" spans="1:2">
       <c r="A444" s="111"/>
       <c r="B444" s="112"/>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="445" spans="1:2">
       <c r="A445" s="111"/>
       <c r="B445" s="112"/>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="446" spans="1:2">
       <c r="A446" s="111"/>
       <c r="B446" s="112"/>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="447" spans="1:2">
       <c r="A447" s="111"/>
       <c r="B447" s="112"/>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="448" spans="1:2">
       <c r="A448" s="111"/>
       <c r="B448" s="112"/>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="449" spans="1:2">
       <c r="A449" s="111"/>
       <c r="B449" s="112"/>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="450" spans="1:2">
       <c r="A450" s="111"/>
       <c r="B450" s="112"/>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="451" spans="1:2">
       <c r="A451" s="111"/>
       <c r="B451" s="112"/>
     </row>
-    <row r="452" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="452" spans="1:2" ht="16.5" customHeight="1">
       <c r="A452" s="111"/>
       <c r="B452" s="112"/>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="453" spans="1:2">
       <c r="A453" s="111"/>
       <c r="B453" s="112"/>
     </row>
-    <row r="454" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="454" spans="1:2" ht="16.5" customHeight="1">
       <c r="A454" s="111"/>
       <c r="B454" s="112"/>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="455" spans="1:2">
       <c r="A455" s="111"/>
       <c r="B455" s="112"/>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="456" spans="1:2">
       <c r="A456" s="111"/>
       <c r="B456" s="112"/>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="457" spans="1:2">
       <c r="A457" s="111"/>
       <c r="B457" s="112"/>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="458" spans="1:2">
       <c r="A458" s="111"/>
       <c r="B458" s="112"/>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="459" spans="1:2">
       <c r="A459" s="111"/>
       <c r="B459" s="112"/>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="460" spans="1:2">
       <c r="A460" s="111"/>
       <c r="B460" s="112"/>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="461" spans="1:2">
       <c r="A461" s="111"/>
       <c r="B461" s="112"/>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="462" spans="1:2">
       <c r="A462" s="111"/>
       <c r="B462" s="112"/>
     </row>
-    <row r="463" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="463" spans="1:2" ht="16.5" customHeight="1">
       <c r="A463" s="111"/>
       <c r="B463" s="112"/>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="464" spans="1:2">
       <c r="A464" s="111"/>
       <c r="B464" s="112"/>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="465" spans="1:2">
       <c r="A465" s="111"/>
       <c r="B465" s="112"/>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="466" spans="1:2">
       <c r="A466" s="111"/>
       <c r="B466" s="112"/>
     </row>
-    <row r="467" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="467" spans="1:2" ht="16.5" customHeight="1">
       <c r="A467" s="111"/>
       <c r="B467" s="112"/>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="468" spans="1:2">
       <c r="A468" s="111"/>
       <c r="B468" s="112"/>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="469" spans="1:2">
       <c r="A469" s="111"/>
       <c r="B469" s="112"/>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="470" spans="1:2">
       <c r="A470" s="111"/>
       <c r="B470" s="112"/>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="471" spans="1:2">
       <c r="A471" s="111"/>
       <c r="B471" s="112"/>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="472" spans="1:2">
       <c r="A472" s="111"/>
       <c r="B472" s="112"/>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="473" spans="1:2">
       <c r="A473" s="111"/>
       <c r="B473" s="112"/>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="474" spans="1:2">
       <c r="A474" s="111"/>
       <c r="B474" s="112"/>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="475" spans="1:2">
       <c r="A475" s="111"/>
       <c r="B475" s="112"/>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="476" spans="1:2">
       <c r="A476" s="111"/>
       <c r="B476" s="112"/>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="477" spans="1:2">
       <c r="A477" s="111"/>
       <c r="B477" s="112"/>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="478" spans="1:2">
       <c r="A478" s="111"/>
       <c r="B478" s="112"/>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="479" spans="1:2">
       <c r="A479" s="111"/>
       <c r="B479" s="112"/>
     </row>
-    <row r="480" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="480" spans="1:2" ht="16.5" customHeight="1">
       <c r="A480" s="111"/>
       <c r="B480" s="112"/>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="481" spans="1:2">
       <c r="A481" s="111"/>
       <c r="B481" s="112"/>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="482" spans="1:2">
       <c r="A482" s="111"/>
       <c r="B482" s="112"/>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="483" spans="1:2">
       <c r="A483" s="111"/>
       <c r="B483" s="112"/>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="484" spans="1:2">
       <c r="A484" s="111"/>
       <c r="B484" s="112"/>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="485" spans="1:2">
       <c r="A485" s="111"/>
       <c r="B485" s="112"/>
     </row>
-    <row r="486" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="486" spans="1:2" ht="30" customHeight="1">
       <c r="A486" s="111"/>
       <c r="B486" s="112"/>
     </row>
-    <row r="487" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="487" spans="1:2" ht="30" customHeight="1">
       <c r="A487" s="111"/>
       <c r="B487" s="112"/>
     </row>
-    <row r="488" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="488" spans="1:2" ht="16.5" customHeight="1">
       <c r="A488" s="111"/>
       <c r="B488" s="112"/>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="489" spans="1:2">
       <c r="A489" s="111"/>
       <c r="B489" s="112"/>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="490" spans="1:2">
       <c r="A490" s="111"/>
       <c r="B490" s="112"/>
     </row>
-    <row r="491" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="491" spans="1:2" ht="16.5" customHeight="1">
       <c r="A491" s="111"/>
       <c r="B491" s="112"/>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="492" spans="1:2">
       <c r="A492" s="111"/>
       <c r="B492" s="112"/>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="493" spans="1:2">
       <c r="A493" s="111"/>
       <c r="B493" s="112"/>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="494" spans="1:2">
       <c r="A494" s="111"/>
       <c r="B494" s="112"/>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="495" spans="1:2">
       <c r="A495" s="111"/>
       <c r="B495" s="112"/>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="496" spans="1:2">
       <c r="A496" s="111"/>
       <c r="B496" s="112"/>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="497" spans="1:2">
       <c r="A497" s="111"/>
       <c r="B497" s="112"/>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="498" spans="1:2">
       <c r="A498" s="111"/>
       <c r="B498" s="112"/>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="499" spans="1:2">
       <c r="A499" s="111"/>
       <c r="B499" s="112"/>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="500" spans="1:2">
       <c r="A500" s="111"/>
       <c r="B500" s="112"/>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="501" spans="1:2">
       <c r="A501" s="111"/>
       <c r="B501" s="112"/>
     </row>
-    <row r="502" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="502" spans="1:2" ht="17.25" customHeight="1">
       <c r="A502" s="111"/>
       <c r="B502" s="112"/>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="503" spans="1:2">
       <c r="A503" s="111"/>
       <c r="B503" s="112"/>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="504" spans="1:2">
       <c r="A504" s="111"/>
       <c r="B504" s="112"/>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="505" spans="1:2">
       <c r="A505" s="111"/>
       <c r="B505" s="112"/>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="506" spans="1:2">
       <c r="A506" s="111"/>
       <c r="B506" s="112"/>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="507" spans="1:2">
       <c r="A507" s="111"/>
       <c r="B507" s="112"/>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="508" spans="1:2">
       <c r="A508" s="111"/>
       <c r="B508" s="112"/>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="509" spans="1:2">
       <c r="A509" s="111"/>
       <c r="B509" s="112"/>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="510" spans="1:2">
       <c r="A510" s="111"/>
       <c r="B510" s="112"/>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="511" spans="1:2">
       <c r="A511" s="111"/>
       <c r="B511" s="112"/>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="512" spans="1:2">
       <c r="A512" s="111"/>
       <c r="B512" s="112"/>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="513" spans="1:2">
       <c r="A513" s="111"/>
       <c r="B513" s="112"/>
     </row>
-    <row r="514" spans="1:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="514" spans="1:2" ht="50.15" customHeight="1">
       <c r="A514" s="111"/>
       <c r="B514" s="112"/>
     </row>
-    <row r="515" spans="1:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="515" spans="1:2" ht="50.15" customHeight="1">
       <c r="A515" s="111"/>
       <c r="B515" s="112"/>
     </row>
-    <row r="516" spans="1:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="516" spans="1:2" ht="50.15" customHeight="1">
       <c r="A516" s="111"/>
       <c r="B516" s="112"/>
     </row>
-    <row r="517" spans="1:2" ht="50.1" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="517" spans="1:2" ht="50.15" customHeight="1">
       <c r="A517" s="111"/>
       <c r="B517" s="112"/>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="518" spans="1:2">
       <c r="A518" s="111"/>
       <c r="B518" s="112"/>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="519" spans="1:2">
       <c r="A519" s="111"/>
       <c r="B519" s="112"/>
     </row>
-    <row r="520" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="520" spans="1:2" ht="16.5" customHeight="1">
       <c r="A520" s="111"/>
       <c r="B520" s="112"/>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="521" spans="1:2">
       <c r="A521" s="111"/>
       <c r="B521" s="112"/>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="522" spans="1:2">
       <c r="A522" s="111"/>
       <c r="B522" s="112"/>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="523" spans="1:2">
       <c r="A523" s="111"/>
       <c r="B523" s="112"/>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="524" spans="1:2">
       <c r="A524" s="111"/>
       <c r="B524" s="112"/>
     </row>
-    <row r="525" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="525" spans="1:2" ht="16.5" customHeight="1">
       <c r="A525" s="111"/>
       <c r="B525" s="112"/>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="526" spans="1:2">
       <c r="A526" s="111"/>
       <c r="B526" s="112"/>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="527" spans="1:2">
       <c r="A527" s="111"/>
       <c r="B527" s="112"/>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="528" spans="1:2">
       <c r="A528" s="111"/>
       <c r="B528" s="112"/>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="529" spans="1:2">
       <c r="A529" s="111"/>
       <c r="B529" s="112"/>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="530" spans="1:2">
       <c r="A530" s="111"/>
       <c r="B530" s="112"/>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="531" spans="1:2">
       <c r="A531" s="111"/>
       <c r="B531" s="112"/>
     </row>
-    <row r="532" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="532" spans="1:2" ht="16.5" customHeight="1">
       <c r="A532" s="111"/>
       <c r="B532" s="112"/>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="533" spans="1:2">
       <c r="A533" s="111"/>
       <c r="B533" s="112"/>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="534" spans="1:2">
       <c r="A534" s="111"/>
       <c r="B534" s="112"/>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="535" spans="1:2">
       <c r="A535" s="111"/>
       <c r="B535" s="112"/>
     </row>
-    <row r="536" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="536" spans="1:2" ht="33" customHeight="1">
       <c r="A536" s="111"/>
       <c r="B536" s="112"/>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="537" spans="1:2">
       <c r="A537" s="111"/>
       <c r="B537" s="112"/>
     </row>
-    <row r="538" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="538" spans="1:2" ht="16.5" customHeight="1">
       <c r="A538" s="111"/>
       <c r="B538" s="112"/>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="539" spans="1:2">
       <c r="A539" s="111"/>
       <c r="B539" s="112"/>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="540" spans="1:2">
       <c r="A540" s="111"/>
       <c r="B540" s="112"/>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="541" spans="1:2">
       <c r="A541" s="111"/>
       <c r="B541" s="112"/>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="542" spans="1:2">
       <c r="A542" s="111"/>
       <c r="B542" s="112"/>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="543" spans="1:2">
       <c r="A543" s="111"/>
       <c r="B543" s="112"/>
     </row>
-    <row r="544" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="544" spans="1:2" ht="60" customHeight="1">
       <c r="A544" s="111"/>
       <c r="B544" s="112"/>
     </row>
-    <row r="545" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="545" spans="1:2" ht="60" customHeight="1">
       <c r="A545" s="111"/>
       <c r="B545" s="112"/>
     </row>
-    <row r="546" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="546" spans="1:2" ht="60" customHeight="1">
       <c r="A546" s="111"/>
       <c r="B546" s="112"/>
     </row>
-    <row r="547" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="547" spans="1:2" ht="60" customHeight="1">
       <c r="A547" s="111"/>
       <c r="B547" s="112"/>
     </row>
-    <row r="548" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="548" spans="1:2" ht="16.5" customHeight="1">
       <c r="A548" s="111"/>
       <c r="B548" s="112"/>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="549" spans="1:2">
       <c r="A549" s="111"/>
       <c r="B549" s="112"/>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="550" spans="1:2">
       <c r="A550" s="111"/>
       <c r="B550" s="112"/>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="551" spans="1:2">
       <c r="A551" s="111"/>
       <c r="B551" s="112"/>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="552" spans="1:2">
       <c r="A552" s="111"/>
       <c r="B552" s="112"/>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="553" spans="1:2">
       <c r="A553" s="111"/>
       <c r="B553" s="112"/>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="554" spans="1:2">
       <c r="A554" s="111"/>
       <c r="B554" s="112"/>
     </row>
-    <row r="555" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="555" spans="1:2" ht="16.5" customHeight="1">
       <c r="A555" s="111"/>
       <c r="B555" s="112"/>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="556" spans="1:2">
       <c r="A556" s="111"/>
       <c r="B556" s="112"/>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="557" spans="1:2">
       <c r="A557" s="111"/>
       <c r="B557" s="112"/>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="558" spans="1:2">
       <c r="A558" s="111"/>
       <c r="B558" s="112"/>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="559" spans="1:2">
       <c r="A559" s="111"/>
       <c r="B559" s="112"/>
     </row>
-    <row r="560" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="560" spans="1:2" ht="16.5" customHeight="1">
       <c r="A560" s="111"/>
       <c r="B560" s="112"/>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="561" spans="1:2">
       <c r="A561" s="111"/>
       <c r="B561" s="112"/>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="562" spans="1:2">
       <c r="A562" s="111"/>
       <c r="B562" s="112"/>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="563" spans="1:2">
       <c r="A563" s="111"/>
       <c r="B563" s="112"/>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="564" spans="1:2">
       <c r="A564" s="111"/>
       <c r="B564" s="112"/>
     </row>
-    <row r="565" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="565" spans="1:2" ht="16.5" customHeight="1">
       <c r="A565" s="111"/>
       <c r="B565" s="112"/>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="566" spans="1:2">
       <c r="A566" s="111"/>
       <c r="B566" s="112"/>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="567" spans="1:2">
       <c r="A567" s="111"/>
       <c r="B567" s="112"/>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="568" spans="1:2">
       <c r="A568" s="111"/>
       <c r="B568" s="112"/>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="569" spans="1:2">
       <c r="A569" s="111"/>
       <c r="B569" s="112"/>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="570" spans="1:2">
       <c r="A570" s="111"/>
       <c r="B570" s="112"/>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="571" spans="1:2">
       <c r="A571" s="111"/>
       <c r="B571" s="112"/>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="572" spans="1:2">
       <c r="A572" s="111"/>
       <c r="B572" s="112"/>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="573" spans="1:2">
       <c r="A573" s="111"/>
       <c r="B573" s="112"/>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="574" spans="1:2">
       <c r="A574" s="111"/>
       <c r="B574" s="112"/>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="575" spans="1:2">
       <c r="A575" s="111"/>
       <c r="B575" s="112"/>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="576" spans="1:2">
       <c r="A576" s="111"/>
       <c r="B576" s="112"/>
     </row>
-    <row r="577" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="577" spans="1:2" ht="30" customHeight="1">
       <c r="A577" s="111"/>
       <c r="B577" s="112"/>
     </row>
-    <row r="578" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="578" spans="1:2" ht="30" customHeight="1">
       <c r="A578" s="111"/>
       <c r="B578" s="112"/>
     </row>
-    <row r="579" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="579" spans="1:2" ht="30" customHeight="1">
       <c r="A579" s="111"/>
       <c r="B579" s="112"/>
     </row>
-    <row r="580" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="580" spans="1:2" ht="30" customHeight="1">
       <c r="A580" s="111"/>
       <c r="B580" s="112"/>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="581" spans="1:2">
       <c r="A581" s="111"/>
       <c r="B581" s="112"/>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="582" spans="1:2">
       <c r="A582" s="111"/>
       <c r="B582" s="112"/>
     </row>
-    <row r="583" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="583" spans="1:2" ht="17.25" customHeight="1">
       <c r="A583" s="111"/>
       <c r="B583" s="112"/>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="584" spans="1:2">
       <c r="A584" s="111"/>
       <c r="B584" s="112"/>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="585" spans="1:2">
       <c r="A585" s="111"/>
       <c r="B585" s="112"/>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="586" spans="1:2">
       <c r="A586" s="111"/>
       <c r="B586" s="112"/>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="587" spans="1:2">
       <c r="A587" s="111"/>
       <c r="B587" s="112"/>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="588" spans="1:2">
       <c r="A588" s="111"/>
       <c r="B588" s="112"/>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="589" spans="1:2">
       <c r="A589" s="111"/>
       <c r="B589" s="112"/>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="590" spans="1:2">
       <c r="A590" s="111"/>
       <c r="B590" s="112"/>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="591" spans="1:2">
       <c r="A591" s="111"/>
       <c r="B591" s="112"/>
     </row>
-    <row r="592" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="592" spans="1:2" ht="16.5" customHeight="1">
       <c r="A592" s="111"/>
       <c r="B592" s="112"/>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="593" spans="1:2">
       <c r="A593" s="111"/>
       <c r="B593" s="112"/>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="594" spans="1:2">
       <c r="A594" s="111"/>
       <c r="B594" s="112"/>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="595" spans="1:2">
       <c r="A595" s="111"/>
       <c r="B595" s="112"/>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="596" spans="1:2">
       <c r="A596" s="111"/>
       <c r="B596" s="112"/>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="597" spans="1:2">
       <c r="A597" s="111"/>
       <c r="B597" s="112"/>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="598" spans="1:2">
       <c r="A598" s="111"/>
       <c r="B598" s="112"/>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="599" spans="1:2">
       <c r="A599" s="111"/>
       <c r="B599" s="112"/>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="600" spans="1:2">
       <c r="A600" s="111"/>
       <c r="B600" s="112"/>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="601" spans="1:2">
       <c r="A601" s="111"/>
       <c r="B601" s="112"/>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="602" spans="1:2">
       <c r="A602" s="111"/>
       <c r="B602" s="112"/>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="603" spans="1:2">
       <c r="A603" s="111"/>
       <c r="B603" s="112"/>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="604" spans="1:2">
       <c r="A604" s="111"/>
       <c r="B604" s="112"/>
     </row>
-    <row r="605" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="605" spans="1:2" ht="16.5" customHeight="1">
       <c r="A605" s="111"/>
       <c r="B605" s="112"/>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="606" spans="1:2">
       <c r="A606" s="111"/>
       <c r="B606" s="112"/>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="607" spans="1:2">
       <c r="A607" s="111"/>
       <c r="B607" s="112"/>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="608" spans="1:2">
       <c r="A608" s="111"/>
       <c r="B608" s="112"/>
     </row>
-    <row r="609" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="609" spans="1:2" ht="16.5" customHeight="1">
       <c r="A609" s="111"/>
       <c r="B609" s="112"/>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="610" spans="1:2">
       <c r="A610" s="111"/>
       <c r="B610" s="112"/>
     </row>
-    <row r="611" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="611" spans="1:2" ht="16.5" customHeight="1">
       <c r="A611" s="111"/>
       <c r="B611" s="112"/>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="612" spans="1:2">
       <c r="A612" s="111"/>
       <c r="B612" s="112"/>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="613" spans="1:2">
       <c r="A613" s="111"/>
       <c r="B613" s="112"/>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="614" spans="1:2">
       <c r="A614" s="111"/>
       <c r="B614" s="112"/>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="615" spans="1:2">
       <c r="A615" s="111"/>
       <c r="B615" s="112"/>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="616" spans="1:2">
       <c r="A616" s="111"/>
       <c r="B616" s="112"/>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="617" spans="1:2">
       <c r="A617" s="111"/>
       <c r="B617" s="112"/>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="618" spans="1:2">
       <c r="A618" s="111"/>
       <c r="B618" s="112"/>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="619" spans="1:2">
       <c r="A619" s="111"/>
       <c r="B619" s="112"/>
     </row>
-    <row r="620" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="620" spans="1:2" ht="16.5" customHeight="1">
       <c r="A620" s="111"/>
       <c r="B620" s="112"/>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="621" spans="1:2">
       <c r="A621" s="111"/>
       <c r="B621" s="112"/>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="622" spans="1:2">
       <c r="A622" s="111"/>
       <c r="B622" s="112"/>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="623" spans="1:2">
       <c r="A623" s="111"/>
       <c r="B623" s="112"/>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="624" spans="1:2">
       <c r="A624" s="111"/>
       <c r="B624" s="112"/>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="625" spans="1:2">
       <c r="A625" s="111"/>
       <c r="B625" s="112"/>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="626" spans="1:2">
       <c r="A626" s="111"/>
       <c r="B626" s="112"/>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="627" spans="1:2">
       <c r="A627" s="111"/>
       <c r="B627" s="112"/>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="628" spans="1:2">
       <c r="A628" s="111"/>
       <c r="B628" s="112"/>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="629" spans="1:2">
       <c r="A629" s="111"/>
       <c r="B629" s="112"/>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="630" spans="1:2">
       <c r="A630" s="111"/>
       <c r="B630" s="112"/>
     </row>
-    <row r="631" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="631" spans="1:2" ht="30" customHeight="1">
       <c r="A631" s="111"/>
       <c r="B631" s="112"/>
     </row>
-    <row r="632" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="632" spans="1:2" ht="30" customHeight="1">
       <c r="A632" s="111"/>
       <c r="B632" s="112"/>
     </row>
-    <row r="633" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="633" spans="1:2" ht="30" customHeight="1">
       <c r="A633" s="111"/>
       <c r="B633" s="112"/>
     </row>
-    <row r="634" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="634" spans="1:2" ht="30" customHeight="1">
       <c r="A634" s="111"/>
       <c r="B634" s="112"/>
     </row>
-    <row r="635" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="635" spans="1:2" ht="30" customHeight="1">
       <c r="A635" s="111"/>
       <c r="B635" s="112"/>
     </row>
-    <row r="636" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="636" spans="1:2" ht="30" customHeight="1">
       <c r="A636" s="111"/>
       <c r="B636" s="112"/>
     </row>
-    <row r="637" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="637" spans="1:2" ht="30" customHeight="1">
       <c r="A637" s="111"/>
       <c r="B637" s="112"/>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="638" spans="1:2">
       <c r="A638" s="111"/>
       <c r="B638" s="112"/>
     </row>
-    <row r="639" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="639" spans="1:2" ht="16.5" customHeight="1">
       <c r="A639" s="111"/>
       <c r="B639" s="112"/>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="640" spans="1:2">
       <c r="A640" s="111"/>
       <c r="B640" s="112"/>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="641" spans="1:2">
       <c r="A641" s="111"/>
       <c r="B641" s="112"/>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="642" spans="1:2">
       <c r="A642" s="111"/>
       <c r="B642" s="112"/>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="643" spans="1:2">
       <c r="A643" s="111"/>
       <c r="B643" s="112"/>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="644" spans="1:2">
       <c r="A644" s="111"/>
       <c r="B644" s="112"/>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="645" spans="1:2">
       <c r="A645" s="111"/>
       <c r="B645" s="112"/>
     </row>
-    <row r="646" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="646" spans="1:2" ht="16.5" customHeight="1">
       <c r="A646" s="111"/>
       <c r="B646" s="112"/>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="647" spans="1:2">
       <c r="A647" s="111"/>
       <c r="B647" s="112"/>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="648" spans="1:2">
       <c r="A648" s="111"/>
       <c r="B648" s="112"/>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="649" spans="1:2">
       <c r="A649" s="111"/>
       <c r="B649" s="112"/>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="650" spans="1:2">
       <c r="A650" s="111"/>
       <c r="B650" s="112"/>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="651" spans="1:2">
       <c r="A651" s="111"/>
       <c r="B651" s="112"/>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="652" spans="1:2">
       <c r="A652" s="111"/>
       <c r="B652" s="112"/>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="653" spans="1:2">
       <c r="A653" s="111"/>
       <c r="B653" s="112"/>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="654" spans="1:2">
       <c r="A654" s="111"/>
       <c r="B654" s="112"/>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="655" spans="1:2">
       <c r="A655" s="111"/>
       <c r="B655" s="112"/>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="656" spans="1:2">
       <c r="A656" s="111"/>
       <c r="B656" s="112"/>
     </row>
-    <row r="657" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="657" spans="1:2" ht="16.5" customHeight="1">
       <c r="A657" s="111"/>
       <c r="B657" s="112"/>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="658" spans="1:2">
       <c r="A658" s="111"/>
       <c r="B658" s="112"/>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="659" spans="1:2">
       <c r="A659" s="111"/>
       <c r="B659" s="112"/>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="660" spans="1:2">
       <c r="A660" s="111"/>
       <c r="B660" s="112"/>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="661" spans="1:2">
       <c r="A661" s="111"/>
       <c r="B661" s="112"/>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="662" spans="1:2">
       <c r="A662" s="111"/>
       <c r="B662" s="112"/>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="663" spans="1:2">
       <c r="A663" s="111"/>
       <c r="B663" s="112"/>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="664" spans="1:2">
       <c r="A664" s="111"/>
       <c r="B664" s="112"/>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="665" spans="1:2">
       <c r="A665" s="111"/>
       <c r="B665" s="112"/>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="666" spans="1:2">
       <c r="A666" s="111"/>
       <c r="B666" s="112"/>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="667" spans="1:2">
       <c r="A667" s="111"/>
       <c r="B667" s="112"/>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="668" spans="1:2">
       <c r="A668" s="111"/>
       <c r="B668" s="112"/>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="669" spans="1:2">
       <c r="A669" s="111"/>
       <c r="B669" s="112"/>
     </row>
-    <row r="670" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="670" spans="1:2" ht="16.5" customHeight="1">
       <c r="A670" s="111"/>
       <c r="B670" s="112"/>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="671" spans="1:2">
       <c r="A671" s="111"/>
       <c r="B671" s="112"/>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="672" spans="1:2">
       <c r="A672" s="111"/>
       <c r="B672" s="112"/>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="673" spans="1:2">
       <c r="A673" s="111"/>
       <c r="B673" s="112"/>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="674" spans="1:2">
       <c r="A674" s="111"/>
       <c r="B674" s="112"/>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="675" spans="1:2">
       <c r="A675" s="111"/>
       <c r="B675" s="112"/>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="676" spans="1:2">
       <c r="A676" s="111"/>
       <c r="B676" s="112"/>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="677" spans="1:2">
       <c r="A677" s="111"/>
       <c r="B677" s="112"/>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="678" spans="1:2">
       <c r="A678" s="111"/>
       <c r="B678" s="112"/>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="679" spans="1:2">
       <c r="A679" s="111"/>
       <c r="B679" s="112"/>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="680" spans="1:2">
       <c r="A680" s="111"/>
       <c r="B680" s="112"/>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="681" spans="1:2">
       <c r="A681" s="111"/>
       <c r="B681" s="112"/>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="682" spans="1:2">
       <c r="A682" s="111"/>
       <c r="B682" s="112"/>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="683" spans="1:2">
       <c r="A683" s="111"/>
       <c r="B683" s="112"/>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="684" spans="1:2">
       <c r="A684" s="111"/>
       <c r="B684" s="112"/>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="685" spans="1:2">
       <c r="A685" s="111"/>
       <c r="B685" s="112"/>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="686" spans="1:2">
       <c r="A686" s="111"/>
       <c r="B686" s="112"/>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="687" spans="1:2">
       <c r="A687" s="111"/>
       <c r="B687" s="112"/>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="688" spans="1:2">
       <c r="A688" s="111"/>
       <c r="B688" s="112"/>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="689" spans="1:2">
       <c r="A689" s="111"/>
       <c r="B689" s="112"/>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="690" spans="1:2">
       <c r="A690" s="111"/>
       <c r="B690" s="112"/>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="691" spans="1:2">
       <c r="A691" s="111"/>
       <c r="B691" s="112"/>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="692" spans="1:2">
       <c r="A692" s="111"/>
       <c r="B692" s="112"/>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="693" spans="1:2">
       <c r="A693" s="111"/>
       <c r="B693" s="112"/>
     </row>
-    <row r="694" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="694" spans="1:2" ht="16.5" customHeight="1">
       <c r="A694" s="111"/>
       <c r="B694" s="112"/>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="695" spans="1:2">
       <c r="A695" s="111"/>
       <c r="B695" s="112"/>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="696" spans="1:2">
       <c r="A696" s="111"/>
       <c r="B696" s="112"/>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="697" spans="1:2">
       <c r="A697" s="111"/>
       <c r="B697" s="112"/>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="698" spans="1:2">
       <c r="A698" s="111"/>
       <c r="B698" s="112"/>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="699" spans="1:2">
       <c r="A699" s="111"/>
       <c r="B699" s="112"/>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="700" spans="1:2">
       <c r="A700" s="111"/>
       <c r="B700" s="112"/>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="701" spans="1:2">
       <c r="A701" s="111"/>
       <c r="B701" s="112"/>
     </row>
-    <row r="702" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="702" spans="1:2" ht="16.5" customHeight="1">
       <c r="A702" s="111"/>
       <c r="B702" s="112"/>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="703" spans="1:2">
       <c r="A703" s="111"/>
       <c r="B703" s="112"/>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="704" spans="1:2">
       <c r="A704" s="111"/>
       <c r="B704" s="112"/>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="705" spans="1:2">
       <c r="A705" s="111"/>
       <c r="B705" s="112"/>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="706" spans="1:2">
       <c r="A706" s="111"/>
       <c r="B706" s="112"/>
     </row>
-    <row r="707" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="707" spans="1:2" ht="16.5" customHeight="1">
       <c r="A707" s="111"/>
       <c r="B707" s="112"/>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="708" spans="1:2">
       <c r="A708" s="111"/>
       <c r="B708" s="112"/>
     </row>
-    <row r="709" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="709" spans="1:2" ht="16.5" customHeight="1">
       <c r="A709" s="111"/>
       <c r="B709" s="112"/>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="710" spans="1:2">
       <c r="A710" s="111"/>
       <c r="B710" s="112"/>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="711" spans="1:2">
       <c r="A711" s="111"/>
       <c r="B711" s="112"/>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="712" spans="1:2">
       <c r="A712" s="111"/>
       <c r="B712" s="112"/>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="713" spans="1:2">
       <c r="A713" s="111"/>
       <c r="B713" s="112"/>
     </row>
-    <row r="714" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="714" spans="1:2" ht="16.5" customHeight="1">
       <c r="A714" s="111"/>
       <c r="B714" s="112"/>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="715" spans="1:2">
       <c r="A715" s="111"/>
       <c r="B715" s="112"/>
     </row>
-    <row r="716" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="716" spans="1:2" ht="16.5" customHeight="1">
       <c r="A716" s="111"/>
       <c r="B716" s="112"/>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="717" spans="1:2">
       <c r="A717" s="111"/>
       <c r="B717" s="112"/>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="718" spans="1:2">
       <c r="A718" s="111"/>
       <c r="B718" s="112"/>
     </row>
-    <row r="719" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="719" spans="1:2" ht="16.5" customHeight="1">
       <c r="A719" s="111"/>
       <c r="B719" s="112"/>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="720" spans="1:2">
       <c r="A720" s="111"/>
       <c r="B720" s="112"/>
     </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="721" spans="1:2">
       <c r="A721" s="111"/>
       <c r="B721" s="112"/>
     </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="722" spans="1:2">
       <c r="A722" s="111"/>
       <c r="B722" s="112"/>
     </row>
-    <row r="723" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="723" spans="1:2" ht="16.5" customHeight="1">
       <c r="A723" s="111"/>
       <c r="B723" s="112"/>
     </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="724" spans="1:2">
       <c r="A724" s="111"/>
       <c r="B724" s="112"/>
     </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="725" spans="1:2">
       <c r="A725" s="111"/>
       <c r="B725" s="112"/>
     </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="726" spans="1:2">
       <c r="A726" s="111"/>
       <c r="B726" s="112"/>
     </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="727" spans="1:2">
       <c r="A727" s="111"/>
       <c r="B727" s="112"/>
     </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="728" spans="1:2">
       <c r="A728" s="111"/>
       <c r="B728" s="112"/>
     </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="729" spans="1:2">
       <c r="A729" s="111"/>
       <c r="B729" s="112"/>
     </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="730" spans="1:2">
       <c r="A730" s="111"/>
       <c r="B730" s="112"/>
     </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="731" spans="1:2">
       <c r="A731" s="111"/>
       <c r="B731" s="112"/>
     </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="732" spans="1:2">
       <c r="A732" s="111"/>
       <c r="B732" s="112"/>
     </row>
-    <row r="733" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="733" spans="1:2" ht="16.5" customHeight="1">
       <c r="A733" s="111"/>
       <c r="B733" s="112"/>
     </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="734" spans="1:2">
       <c r="A734" s="111"/>
       <c r="B734" s="112"/>
     </row>
-    <row r="735" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="735" spans="1:2" ht="16.5" customHeight="1">
       <c r="A735" s="111"/>
       <c r="B735" s="112"/>
     </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="736" spans="1:2">
       <c r="A736" s="111"/>
       <c r="B736" s="112"/>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="737" spans="1:2">
       <c r="A737" s="111"/>
       <c r="B737" s="112"/>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="738" spans="1:2">
       <c r="A738" s="111"/>
       <c r="B738" s="112"/>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="739" spans="1:2">
       <c r="A739" s="111"/>
       <c r="B739" s="112"/>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="740" spans="1:2">
       <c r="A740" s="111"/>
       <c r="B740" s="112"/>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="741" spans="1:2">
       <c r="A741" s="111"/>
       <c r="B741" s="112"/>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="742" spans="1:2">
       <c r="A742" s="111"/>
       <c r="B742" s="112"/>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="743" spans="1:2">
       <c r="A743" s="111"/>
       <c r="B743" s="112"/>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="744" spans="1:2">
       <c r="A744" s="111"/>
       <c r="B744" s="112"/>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="745" spans="1:2">
       <c r="A745" s="111"/>
       <c r="B745" s="112"/>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="746" spans="1:2">
       <c r="A746" s="111"/>
       <c r="B746" s="112"/>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="747" spans="1:2">
       <c r="A747" s="111"/>
       <c r="B747" s="112"/>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="748" spans="1:2">
       <c r="A748" s="111"/>
       <c r="B748" s="112"/>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="749" spans="1:2">
       <c r="A749" s="111"/>
       <c r="B749" s="112"/>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="750" spans="1:2">
       <c r="A750" s="111"/>
       <c r="B750" s="112"/>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="751" spans="1:2">
       <c r="A751" s="111"/>
       <c r="B751" s="112"/>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="752" spans="1:2">
       <c r="A752" s="111"/>
       <c r="B752" s="112"/>
     </row>
-    <row r="753" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="753" spans="1:2" ht="17.25" customHeight="1">
       <c r="A753" s="111"/>
       <c r="B753" s="112"/>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="754" spans="1:2">
       <c r="A754" s="111"/>
       <c r="B754" s="112"/>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="755" spans="1:2">
       <c r="A755" s="111"/>
       <c r="B755" s="112"/>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="756" spans="1:2">
       <c r="A756" s="111"/>
       <c r="B756" s="112"/>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="757" spans="1:2">
       <c r="A757" s="111"/>
       <c r="B757" s="112"/>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="758" spans="1:2">
       <c r="A758" s="111"/>
       <c r="B758" s="112"/>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="759" spans="1:2">
       <c r="A759" s="111"/>
       <c r="B759" s="112"/>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="760" spans="1:2">
       <c r="A760" s="111"/>
       <c r="B760" s="112"/>
     </row>
-    <row r="761" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="761" spans="1:2" ht="16.5" customHeight="1">
       <c r="A761" s="111"/>
       <c r="B761" s="112"/>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="762" spans="1:2">
       <c r="A762" s="111"/>
       <c r="B762" s="112"/>
     </row>
-    <row r="763" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="763" spans="1:2" ht="16.5" customHeight="1">
       <c r="A763" s="111"/>
       <c r="B763" s="112"/>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="764" spans="1:2">
       <c r="A764" s="111"/>
       <c r="B764" s="112"/>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="765" spans="1:2">
       <c r="A765" s="111"/>
       <c r="B765" s="112"/>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="766" spans="1:2">
       <c r="A766" s="111"/>
       <c r="B766" s="112"/>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="767" spans="1:2">
       <c r="A767" s="111"/>
       <c r="B767" s="112"/>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="768" spans="1:2">
       <c r="A768" s="111"/>
       <c r="B768" s="112"/>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="769" spans="1:2">
       <c r="A769" s="111"/>
       <c r="B769" s="112"/>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="770" spans="1:2">
       <c r="A770" s="111"/>
       <c r="B770" s="112"/>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="771" spans="1:2">
       <c r="A771" s="111"/>
       <c r="B771" s="112"/>
     </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="772" spans="1:2">
       <c r="A772" s="111"/>
       <c r="B772" s="112"/>
     </row>
-    <row r="773" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="773" spans="1:2" ht="16.5" customHeight="1">
       <c r="A773" s="111"/>
       <c r="B773" s="112"/>
     </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="774" spans="1:2">
       <c r="A774" s="111"/>
       <c r="B774" s="112"/>
     </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="775" spans="1:2">
       <c r="A775" s="111"/>
       <c r="B775" s="112"/>
     </row>
-    <row r="776" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="776" spans="1:2" ht="16.5" customHeight="1">
       <c r="A776" s="111"/>
       <c r="B776" s="112"/>
     </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="777" spans="1:2">
       <c r="A777" s="111"/>
       <c r="B777" s="112"/>
     </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="778" spans="1:2">
       <c r="A778" s="111"/>
       <c r="B778" s="112"/>
     </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="779" spans="1:2">
       <c r="A779" s="111"/>
       <c r="B779" s="112"/>
     </row>
-    <row r="780" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="780" spans="1:2">
       <c r="A780" s="111"/>
       <c r="B780" s="112"/>
     </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="781" spans="1:2">
       <c r="A781" s="111"/>
       <c r="B781" s="112"/>
     </row>
-    <row r="782" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="782" spans="1:2" ht="16.5" customHeight="1">
       <c r="A782" s="111"/>
       <c r="B782" s="112"/>
     </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="783" spans="1:2">
       <c r="A783" s="111"/>
       <c r="B783" s="112"/>
     </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="784" spans="1:2">
       <c r="A784" s="111"/>
       <c r="B784" s="112"/>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="785" spans="1:2">
       <c r="A785" s="111"/>
       <c r="B785" s="112"/>
     </row>
-    <row r="786" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="786" spans="1:2" ht="16.5" customHeight="1">
       <c r="A786" s="111"/>
       <c r="B786" s="112"/>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="787" spans="1:2">
       <c r="A787" s="111"/>
       <c r="B787" s="112"/>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="788" spans="1:2">
       <c r="A788" s="111"/>
       <c r="B788" s="112"/>
     </row>
-    <row r="789" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="789" spans="1:2" ht="16.5" customHeight="1">
       <c r="A789" s="111"/>
       <c r="B789" s="112"/>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="790" spans="1:2">
       <c r="A790" s="111"/>
       <c r="B790" s="112"/>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="791" spans="1:2">
       <c r="A791" s="111"/>
       <c r="B791" s="112"/>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="792" spans="1:2">
       <c r="A792" s="111"/>
       <c r="B792" s="112"/>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="793" spans="1:2">
       <c r="A793" s="111"/>
       <c r="B793" s="112"/>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="794" spans="1:2">
       <c r="A794" s="111"/>
       <c r="B794" s="112"/>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="795" spans="1:2">
       <c r="A795" s="111"/>
       <c r="B795" s="112"/>
     </row>
-    <row r="796" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="796" spans="1:2" ht="16.5" customHeight="1">
       <c r="A796" s="111"/>
       <c r="B796" s="112"/>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="797" spans="1:2">
       <c r="A797" s="111"/>
       <c r="B797" s="112"/>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="798" spans="1:2">
       <c r="A798" s="111"/>
       <c r="B798" s="112"/>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="799" spans="1:2">
       <c r="A799" s="111"/>
       <c r="B799" s="112"/>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="800" spans="1:2">
       <c r="A800" s="111"/>
       <c r="B800" s="112"/>
     </row>
-    <row r="801" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="801" spans="1:2">
       <c r="A801" s="111"/>
       <c r="B801" s="112"/>
     </row>
-    <row r="802" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="802" spans="1:2">
       <c r="A802" s="111"/>
       <c r="B802" s="112"/>
     </row>
-    <row r="803" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="803" spans="1:2">
       <c r="A803" s="111"/>
       <c r="B803" s="112"/>
     </row>
-    <row r="804" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="804" spans="1:2">
       <c r="A804" s="111"/>
       <c r="B804" s="112"/>
     </row>
-    <row r="805" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="805" spans="1:2" ht="17.25" customHeight="1">
       <c r="A805" s="111"/>
       <c r="B805" s="112"/>
     </row>
-    <row r="806" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="806" spans="1:2">
       <c r="A806" s="111"/>
       <c r="B806" s="112"/>
     </row>
-    <row r="807" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="807" spans="1:2">
       <c r="A807" s="111"/>
       <c r="B807" s="112"/>
     </row>
-    <row r="808" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="808" spans="1:2">
       <c r="A808" s="111"/>
       <c r="B808" s="112"/>
     </row>
-    <row r="809" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="809" spans="1:2">
       <c r="A809" s="111"/>
       <c r="B809" s="112"/>
     </row>
-    <row r="810" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="810" spans="1:2">
       <c r="A810" s="111"/>
       <c r="B810" s="112"/>
     </row>
-    <row r="811" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="811" spans="1:2">
       <c r="A811" s="111"/>
       <c r="B811" s="112"/>
     </row>
-    <row r="812" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="812" spans="1:2">
       <c r="A812" s="111"/>
       <c r="B812" s="112"/>
     </row>
-    <row r="813" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="813" spans="1:2">
       <c r="A813" s="111"/>
       <c r="B813" s="112"/>
     </row>
-    <row r="814" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="814" spans="1:2">
       <c r="A814" s="111"/>
       <c r="B814" s="112"/>
     </row>
-    <row r="815" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="815" spans="1:2">
       <c r="A815" s="111"/>
       <c r="B815" s="112"/>
     </row>
-    <row r="816" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="816" spans="1:2" ht="16.5" customHeight="1">
       <c r="A816" s="111"/>
       <c r="B816" s="112"/>
     </row>
-    <row r="817" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="817" spans="1:2">
       <c r="A817" s="111"/>
       <c r="B817" s="112"/>
     </row>
-    <row r="818" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="818" spans="1:2">
       <c r="A818" s="111"/>
       <c r="B818" s="112"/>
     </row>
-    <row r="819" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="819" spans="1:2">
       <c r="A819" s="111"/>
       <c r="B819" s="112"/>
     </row>
-    <row r="820" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="820" spans="1:2" ht="16.5" customHeight="1">
       <c r="A820" s="111"/>
       <c r="B820" s="112"/>
     </row>
-    <row r="821" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="821" spans="1:2">
       <c r="A821" s="111"/>
       <c r="B821" s="112"/>
     </row>
-    <row r="822" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="822" spans="1:2">
       <c r="A822" s="111"/>
       <c r="B822" s="112"/>
     </row>
-    <row r="823" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="823" spans="1:2">
       <c r="A823" s="111"/>
       <c r="B823" s="112"/>
     </row>
-    <row r="824" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="824" spans="1:2">
       <c r="A824" s="111"/>
       <c r="B824" s="112"/>
     </row>
-    <row r="825" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="825" spans="1:2">
       <c r="A825" s="111"/>
       <c r="B825" s="112"/>
     </row>
-    <row r="826" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="826" spans="1:2" ht="16.5" customHeight="1">
       <c r="A826" s="111"/>
       <c r="B826" s="112"/>
     </row>
-    <row r="827" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="827" spans="1:2">
       <c r="A827" s="111"/>
       <c r="B827" s="112"/>
     </row>
-    <row r="828" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="828" spans="1:2">
       <c r="A828" s="111"/>
       <c r="B828" s="112"/>
     </row>
-    <row r="829" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="829" spans="1:2">
       <c r="A829" s="111"/>
       <c r="B829" s="112"/>
     </row>
-    <row r="830" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="830" spans="1:2">
       <c r="A830" s="111"/>
       <c r="B830" s="112"/>
     </row>
-    <row r="831" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="831" spans="1:2">
       <c r="A831" s="111"/>
       <c r="B831" s="112"/>
     </row>
-    <row r="832" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="832" spans="1:2">
       <c r="A832" s="111"/>
       <c r="B832" s="112"/>
     </row>
-    <row r="833" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="833" spans="1:2">
       <c r="A833" s="111"/>
       <c r="B833" s="112"/>
     </row>
-    <row r="834" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="834" spans="1:2">
       <c r="A834" s="111"/>
       <c r="B834" s="112"/>
     </row>
-    <row r="835" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="835" spans="1:2">
       <c r="A835" s="111"/>
       <c r="B835" s="112"/>
     </row>
-    <row r="836" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="836" spans="1:2" ht="16.5" customHeight="1">
       <c r="A836" s="111"/>
       <c r="B836" s="112"/>
     </row>
-    <row r="837" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="837" spans="1:2">
       <c r="A837" s="111"/>
       <c r="B837" s="112"/>
     </row>
-    <row r="838" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="838" spans="1:2">
       <c r="A838" s="111"/>
       <c r="B838" s="112"/>
     </row>
-    <row r="839" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="839" spans="1:2">
       <c r="A839" s="111"/>
       <c r="B839" s="112"/>
     </row>
-    <row r="840" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="840" spans="1:2">
       <c r="A840" s="111"/>
       <c r="B840" s="112"/>
     </row>
-    <row r="841" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="841" spans="1:2" ht="16.5" customHeight="1">
       <c r="A841" s="111"/>
       <c r="B841" s="112"/>
     </row>
-    <row r="842" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="842" spans="1:2">
       <c r="A842" s="111"/>
       <c r="B842" s="112"/>
     </row>
-    <row r="843" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="843" spans="1:2">
       <c r="A843" s="111"/>
       <c r="B843" s="112"/>
     </row>
-    <row r="844" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="844" spans="1:2" ht="17.25" customHeight="1">
       <c r="A844" s="111"/>
       <c r="B844" s="112"/>
     </row>
-    <row r="845" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="845" spans="1:2">
       <c r="A845" s="111"/>
       <c r="B845" s="112"/>
     </row>
-    <row r="846" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="846" spans="1:2">
       <c r="A846" s="111"/>
       <c r="B846" s="112"/>
     </row>
-    <row r="847" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="847" spans="1:2">
       <c r="A847" s="111"/>
       <c r="B847" s="112"/>
     </row>
-    <row r="848" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="848" spans="1:2">
       <c r="A848" s="111"/>
       <c r="B848" s="112"/>
     </row>
-    <row r="849" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="849" spans="1:2" ht="16.5" customHeight="1">
       <c r="A849" s="111"/>
       <c r="B849" s="112"/>
     </row>
-    <row r="850" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="850" spans="1:2">
       <c r="A850" s="111"/>
       <c r="B850" s="112"/>
     </row>
-    <row r="851" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="851" spans="1:2">
       <c r="A851" s="111"/>
       <c r="B851" s="112"/>
     </row>
-    <row r="852" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="852" spans="1:2">
       <c r="A852" s="111"/>
       <c r="B852" s="112"/>
     </row>
-    <row r="853" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="853" spans="1:2" ht="16.5" customHeight="1">
       <c r="A853" s="111"/>
       <c r="B853" s="112"/>
     </row>
-    <row r="854" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="854" spans="1:2">
       <c r="A854" s="111"/>
       <c r="B854" s="112"/>
     </row>
-    <row r="855" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="855" spans="1:2">
       <c r="A855" s="111"/>
       <c r="B855" s="112"/>
     </row>
-    <row r="856" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="856" spans="1:2">
       <c r="A856" s="111"/>
       <c r="B856" s="112"/>
     </row>
-    <row r="857" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="857" spans="1:2">
       <c r="A857" s="111"/>
       <c r="B857" s="112"/>
     </row>
-    <row r="858" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="858" spans="1:2">
       <c r="A858" s="111"/>
       <c r="B858" s="112"/>
     </row>
-    <row r="859" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="859" spans="1:2">
       <c r="A859" s="111"/>
       <c r="B859" s="112"/>
     </row>
-    <row r="860" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="860" spans="1:2" ht="16.5" customHeight="1">
       <c r="A860" s="111"/>
       <c r="B860" s="112"/>
     </row>
-    <row r="861" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="861" spans="1:2">
       <c r="A861" s="111"/>
       <c r="B861" s="112"/>
     </row>
-    <row r="862" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="862" spans="1:2">
       <c r="A862" s="111"/>
       <c r="B862" s="112"/>
     </row>
-    <row r="863" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="863" spans="1:2">
       <c r="A863" s="111"/>
       <c r="B863" s="112"/>
     </row>
-    <row r="864" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="864" spans="1:2">
       <c r="A864" s="111"/>
       <c r="B864" s="112"/>
     </row>
-    <row r="865" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="865" spans="1:2">
       <c r="A865" s="111"/>
       <c r="B865" s="112"/>
     </row>
-    <row r="866" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="866" spans="1:2">
       <c r="A866" s="111"/>
       <c r="B866" s="112"/>
     </row>
-    <row r="867" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="867" spans="1:2">
       <c r="A867" s="111"/>
       <c r="B867" s="112"/>
     </row>
-    <row r="868" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="868" spans="1:2">
       <c r="A868" s="111"/>
       <c r="B868" s="112"/>
     </row>
-    <row r="869" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="869" spans="1:2">
       <c r="A869" s="111"/>
       <c r="B869" s="112"/>
     </row>
-    <row r="870" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="870" spans="1:2">
       <c r="A870" s="111"/>
       <c r="B870" s="112"/>
     </row>
-    <row r="871" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="871" spans="1:2" ht="16.5" customHeight="1">
       <c r="A871" s="111"/>
       <c r="B871" s="112"/>
     </row>
-    <row r="872" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="872" spans="1:2">
       <c r="A872" s="111"/>
       <c r="B872" s="112"/>
     </row>
-    <row r="873" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="873" spans="1:2">
       <c r="A873" s="111"/>
       <c r="B873" s="112"/>
     </row>
-    <row r="874" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="874" spans="1:2">
       <c r="A874" s="111"/>
       <c r="B874" s="112"/>
     </row>
-    <row r="875" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="875" spans="1:2">
       <c r="A875" s="111"/>
       <c r="B875" s="112"/>
     </row>
-    <row r="876" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="876" spans="1:2">
       <c r="A876" s="111"/>
       <c r="B876" s="112"/>
     </row>
-    <row r="877" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="877" spans="1:2">
       <c r="A877" s="111"/>
       <c r="B877" s="112"/>
     </row>
-    <row r="878" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="878" spans="1:2">
       <c r="A878" s="111"/>
       <c r="B878" s="112"/>
     </row>
-    <row r="879" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="879" spans="1:2">
       <c r="A879" s="111"/>
       <c r="B879" s="112"/>
     </row>
-    <row r="880" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="880" spans="1:2">
       <c r="A880" s="111"/>
       <c r="B880" s="112"/>
     </row>
-    <row r="881" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="881" spans="1:2" ht="16.5" customHeight="1">
       <c r="A881" s="111"/>
       <c r="B881" s="112"/>
     </row>
-    <row r="882" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="882" spans="1:2">
       <c r="A882" s="111"/>
       <c r="B882" s="112"/>
     </row>
-    <row r="883" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="883" spans="1:2">
       <c r="A883" s="111"/>
       <c r="B883" s="112"/>
     </row>
-    <row r="884" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="884" spans="1:2">
       <c r="A884" s="111"/>
       <c r="B884" s="112"/>
     </row>
-    <row r="885" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="885" spans="1:2">
       <c r="A885" s="111"/>
       <c r="B885" s="112"/>
     </row>
-    <row r="886" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="886" spans="1:2">
       <c r="A886" s="111"/>
       <c r="B886" s="112"/>
     </row>
-    <row r="887" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="887" spans="1:2" ht="16.5" customHeight="1">
       <c r="A887" s="111"/>
       <c r="B887" s="112"/>
     </row>
-    <row r="888" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="888" spans="1:2">
       <c r="A888" s="111"/>
       <c r="B888" s="112"/>
     </row>
-    <row r="889" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="889" spans="1:2">
       <c r="A889" s="111"/>
       <c r="B889" s="112"/>
     </row>
-    <row r="890" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="890" spans="1:2">
       <c r="A890" s="111"/>
       <c r="B890" s="112"/>
     </row>
-    <row r="891" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="891" spans="1:2">
       <c r="A891" s="111"/>
       <c r="B891" s="112"/>
     </row>
-    <row r="892" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="892" spans="1:2">
       <c r="A892" s="111"/>
       <c r="B892" s="112"/>
     </row>
-    <row r="893" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="893" spans="1:2">
       <c r="A893" s="111"/>
       <c r="B893" s="112"/>
     </row>
-    <row r="894" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="894" spans="1:2">
       <c r="A894" s="111"/>
       <c r="B894" s="112"/>
     </row>
-    <row r="895" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="895" spans="1:2">
       <c r="A895" s="111"/>
       <c r="B895" s="112"/>
     </row>
-    <row r="896" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="896" spans="1:2">
       <c r="A896" s="111"/>
       <c r="B896" s="112"/>
     </row>
-    <row r="897" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="897" spans="1:2">
       <c r="A897" s="111"/>
       <c r="B897" s="112"/>
     </row>
-    <row r="898" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="898" spans="1:2">
       <c r="A898" s="111"/>
       <c r="B898" s="112"/>
     </row>
-    <row r="899" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="899" spans="1:2">
       <c r="A899" s="111"/>
       <c r="B899" s="112"/>
     </row>
-    <row r="900" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="900" spans="1:2">
       <c r="A900" s="111"/>
       <c r="B900" s="112"/>
     </row>
-    <row r="901" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="901" spans="1:2" ht="30" customHeight="1">
       <c r="A901" s="111"/>
       <c r="B901" s="112"/>
     </row>
-    <row r="902" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="902" spans="1:2" ht="30" customHeight="1">
       <c r="A902" s="111"/>
       <c r="B902" s="112"/>
     </row>
-    <row r="903" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="903" spans="1:2" ht="30" customHeight="1">
       <c r="A903" s="111"/>
       <c r="B903" s="112"/>
     </row>
-    <row r="904" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="904" spans="1:2">
       <c r="A904" s="111"/>
       <c r="B904" s="112"/>
     </row>
-    <row r="905" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="905" spans="1:2">
       <c r="A905" s="111"/>
       <c r="B905" s="112"/>
     </row>
-    <row r="906" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="906" spans="1:2">
       <c r="A906" s="111"/>
       <c r="B906" s="112"/>
     </row>
-    <row r="907" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="907" spans="1:2">
       <c r="A907" s="111"/>
       <c r="B907" s="112"/>
     </row>
-    <row r="911" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="912" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="915" ht="17.25" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="916" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="917" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="918" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="919" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="920" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="921" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="922" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="923" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="924" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="925" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="926" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="927" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="928" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="930" ht="16.5" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="911" spans="1:2" ht="30" customHeight="1"/>
+    <row r="912" spans="1:2" ht="30" customHeight="1"/>
+    <row r="915" ht="17.25" customHeight="1"/>
+    <row r="916" ht="16.5" customHeight="1"/>
+    <row r="917" ht="16.5" customHeight="1"/>
+    <row r="918" ht="16.5" customHeight="1"/>
+    <row r="919" ht="16.5" customHeight="1"/>
+    <row r="920" ht="16.5" customHeight="1"/>
+    <row r="921" ht="16.5" customHeight="1"/>
+    <row r="922" ht="16.5" customHeight="1"/>
+    <row r="923" ht="16.5" customHeight="1"/>
+    <row r="924" ht="16.5" customHeight="1"/>
+    <row r="925" ht="16.5" customHeight="1"/>
+    <row r="926" ht="16.5" customHeight="1"/>
+    <row r="927" ht="16.5" customHeight="1"/>
+    <row r="928" ht="16.5" customHeight="1"/>
+    <row r="930" ht="16.5" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="A1:E197" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="O"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9085,13 +9096,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F213A4A-B708-49BF-9523-D0135F685F07}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="3" max="3" width="46.94921875" customWidth="1"/>
-    <col min="4" max="4" width="61.44921875" customWidth="1"/>
+    <col min="3" max="3" width="46.9140625" customWidth="1"/>
+    <col min="4" max="4" width="61.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:5" ht="34">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -9108,7 +9119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:5" ht="34">
       <c r="A2" s="107">
         <v>1</v>
       </c>
@@ -9125,7 +9136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="165" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:5" ht="170">
       <c r="A3" s="89">
         <v>1</v>
       </c>
@@ -9142,7 +9153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:5" ht="34">
       <c r="A4" s="89">
         <v>1</v>
       </c>
@@ -9159,7 +9170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="66" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:5" ht="68">
       <c r="A5" s="89">
         <v>1</v>
       </c>
@@ -9176,7 +9187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="346.5" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:5" ht="357">
       <c r="A6" s="89">
         <v>1</v>
       </c>
@@ -9193,7 +9204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:5" ht="34">
       <c r="A7" s="89">
         <v>1</v>
       </c>
@@ -9210,7 +9221,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="148.5" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:5" ht="153">
       <c r="A8" s="89">
         <v>1</v>
       </c>
@@ -9227,7 +9238,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="132" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:5" ht="136">
       <c r="A9" s="89">
         <v>1</v>
       </c>
@@ -9244,7 +9255,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="10" spans="1:5" ht="51">
       <c r="A10" s="89">
         <v>1</v>
       </c>
@@ -9261,7 +9272,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+    <row r="11" spans="1:5" ht="34">
       <c r="A11" s="89">
         <v>1</v>
       </c>
@@ -9278,7 +9289,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="82.5" x14ac:dyDescent="0.7">
+    <row r="12" spans="1:5" ht="85">
       <c r="A12" s="89">
         <v>1</v>
       </c>
@@ -9295,7 +9306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="132" x14ac:dyDescent="0.7">
+    <row r="13" spans="1:5" ht="136">
       <c r="A13" s="89">
         <v>1</v>
       </c>
@@ -9312,7 +9323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="148.5" x14ac:dyDescent="0.7">
+    <row r="14" spans="1:5" ht="153">
       <c r="A14" s="89">
         <v>1</v>
       </c>
@@ -9329,7 +9340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="148.5" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:5" ht="153">
       <c r="A15" s="89">
         <v>1</v>
       </c>
@@ -9346,7 +9357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="66" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:5" ht="68">
       <c r="A16" s="89">
         <v>1</v>
       </c>
@@ -9363,7 +9374,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="115.5" x14ac:dyDescent="0.7">
+    <row r="17" spans="1:5" ht="119">
       <c r="A17" s="89">
         <v>1</v>
       </c>
@@ -9380,7 +9391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="165" x14ac:dyDescent="0.7">
+    <row r="18" spans="1:5" ht="170">
       <c r="A18" s="89">
         <v>1</v>
       </c>
@@ -9397,7 +9408,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="181.5" x14ac:dyDescent="0.7">
+    <row r="19" spans="1:5" ht="187">
       <c r="A19" s="89">
         <v>1</v>
       </c>
@@ -9414,7 +9425,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="115.5" x14ac:dyDescent="0.7">
+    <row r="20" spans="1:5" ht="119">
       <c r="A20" s="89">
         <v>1</v>
       </c>
@@ -9431,7 +9442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="21" spans="1:5" ht="51">
       <c r="A21" s="89">
         <v>1</v>
       </c>
@@ -9448,7 +9459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="33" x14ac:dyDescent="0.7">
+    <row r="22" spans="1:5" ht="34">
       <c r="A22" s="89">
         <v>1</v>
       </c>
